--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -145,10 +149,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,6 +158,10 @@
   </si>
   <si>
     <t>PE均值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -185,7 +189,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
+    <t>利润</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -667,7 +671,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -829,6 +833,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -838,7 +845,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -999,6 +1006,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1042,7 +1052,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1204,6 +1214,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1213,7 +1226,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1375,6 +1388,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1681068.5808443392</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1717781.1968650564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1417,7 +1433,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1579,6 +1595,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1588,7 +1607,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1750,6 +1769,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>522575.55136211542</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>559288.16738283262</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1771,11 +1793,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475371392"/>
-        <c:axId val="475372928"/>
+        <c:axId val="523372416"/>
+        <c:axId val="523411840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475371392"/>
+        <c:axId val="523372416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1818,14 +1840,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475372928"/>
+        <c:crossAx val="523411840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475372928"/>
+        <c:axId val="523411840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1876,7 +1898,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475371392"/>
+        <c:crossAx val="523372416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2067,7 +2089,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2229,6 +2251,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2248,8 +2273,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="556030976"/>
-        <c:axId val="556029440"/>
+        <c:axId val="565314688"/>
+        <c:axId val="543423872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2274,7 +2299,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2436,6 +2461,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2445,7 +2473,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2607,6 +2635,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2628,11 +2659,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556026112"/>
-        <c:axId val="556027904"/>
+        <c:axId val="543420800"/>
+        <c:axId val="543422336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556026112"/>
+        <c:axId val="543420800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2675,14 +2706,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556027904"/>
+        <c:crossAx val="543422336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556027904"/>
+        <c:axId val="543422336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2733,12 +2764,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556026112"/>
+        <c:crossAx val="543420800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556029440"/>
+        <c:axId val="543423872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2775,12 +2806,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556030976"/>
+        <c:crossAx val="565314688"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="556030976"/>
+        <c:axId val="565314688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2789,7 +2820,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556029440"/>
+        <c:crossAx val="543423872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2968,7 +2999,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3130,6 +3161,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3139,7 +3173,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3300,6 +3334,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3343,7 +3380,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3505,6 +3542,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3514,7 +3554,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3676,6 +3716,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13294599.184037466</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13593904.720455116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3718,7 +3761,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3880,6 +3923,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3889,7 +3935,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4051,6 +4097,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5018959.1907411907</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5318264.7271588407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4072,11 +4121,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556071168"/>
-        <c:axId val="556716032"/>
+        <c:axId val="565346688"/>
+        <c:axId val="565348224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556071168"/>
+        <c:axId val="565346688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4119,14 +4168,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556716032"/>
+        <c:crossAx val="565348224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556716032"/>
+        <c:axId val="565348224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4226,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556071168"/>
+        <c:crossAx val="565346688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4368,7 +4417,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4530,6 +4579,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-18333.497294467583</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-46393.241034391052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4549,8 +4601,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="556748160"/>
-        <c:axId val="556746624"/>
+        <c:axId val="565372416"/>
+        <c:axId val="565370880"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4575,7 +4627,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4737,6 +4789,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4746,7 +4801,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4908,6 +4963,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4929,11 +4987,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556739200"/>
-        <c:axId val="556745088"/>
+        <c:axId val="565367552"/>
+        <c:axId val="565369088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556739200"/>
+        <c:axId val="565367552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4976,14 +5034,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556745088"/>
+        <c:crossAx val="565369088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556745088"/>
+        <c:axId val="565369088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5034,12 +5092,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556739200"/>
+        <c:crossAx val="565367552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556746624"/>
+        <c:axId val="565370880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5076,12 +5134,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556748160"/>
+        <c:crossAx val="565372416"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="556748160"/>
+        <c:axId val="565372416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5090,7 +5148,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556746624"/>
+        <c:crossAx val="565370880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5269,7 +5327,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5431,6 +5489,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5440,7 +5501,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5601,6 +5662,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5644,7 +5708,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5806,6 +5870,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5815,7 +5882,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5977,6 +6044,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13918241.906652076</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14227459.764016345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6019,7 +6089,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6181,6 +6251,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6190,7 +6263,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6352,6 +6425,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4556907.088924652</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4866124.9462889209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6373,11 +6449,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557234816"/>
-        <c:axId val="557351296"/>
+        <c:axId val="668537984"/>
+        <c:axId val="668539520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557234816"/>
+        <c:axId val="668537984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6420,14 +6496,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557351296"/>
+        <c:crossAx val="668539520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557351296"/>
+        <c:axId val="668539520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6478,7 +6554,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557234816"/>
+        <c:crossAx val="668537984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6669,7 +6745,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6831,6 +6907,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6850,8 +6929,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="557371392"/>
-        <c:axId val="557369600"/>
+        <c:axId val="669341952"/>
+        <c:axId val="669340416"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6876,7 +6955,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7038,6 +7117,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7047,7 +7129,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7209,6 +7291,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7230,11 +7315,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557366272"/>
-        <c:axId val="557368064"/>
+        <c:axId val="668562944"/>
+        <c:axId val="668564480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557366272"/>
+        <c:axId val="668562944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7277,14 +7362,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557368064"/>
+        <c:crossAx val="668564480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557368064"/>
+        <c:axId val="668564480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7335,12 +7420,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557366272"/>
+        <c:crossAx val="668562944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="557369600"/>
+        <c:axId val="669340416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7377,12 +7462,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557371392"/>
+        <c:crossAx val="669341952"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="557371392"/>
+        <c:axId val="669341952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7391,7 +7476,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="557369600"/>
+        <c:crossAx val="669340416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7553,7 +7638,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7715,6 +7800,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7734,8 +7822,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="557341312"/>
-        <c:axId val="557339776"/>
+        <c:axId val="673665792"/>
+        <c:axId val="673639424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7760,7 +7848,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7922,6 +8010,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7931,7 +8022,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8093,6 +8184,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8114,11 +8208,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557335296"/>
-        <c:axId val="557336832"/>
+        <c:axId val="670297088"/>
+        <c:axId val="673637504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557335296"/>
+        <c:axId val="670297088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8161,14 +8255,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557336832"/>
+        <c:crossAx val="673637504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557336832"/>
+        <c:axId val="673637504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8219,12 +8313,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557335296"/>
+        <c:crossAx val="670297088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="557339776"/>
+        <c:axId val="673639424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8261,12 +8355,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557341312"/>
+        <c:crossAx val="673665792"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="557341312"/>
+        <c:axId val="673665792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8369,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="557339776"/>
+        <c:crossAx val="673639424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8454,7 +8548,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8616,6 +8710,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8625,7 +8722,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8786,6 +8883,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8829,7 +8929,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8991,6 +9091,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9000,7 +9103,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9162,6 +9265,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1892332.1802078688</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1934291.8223967806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9204,7 +9310,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9366,6 +9472,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9375,7 +9484,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9537,6 +9646,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>572440.58810827555</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>614400.23029718734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9558,11 +9670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560541056"/>
-        <c:axId val="560555904"/>
+        <c:axId val="676790656"/>
+        <c:axId val="676792576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560541056"/>
+        <c:axId val="676790656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9605,14 +9717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560555904"/>
+        <c:crossAx val="676792576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560555904"/>
+        <c:axId val="676792576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9663,7 +9775,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560541056"/>
+        <c:crossAx val="676790656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9875,7 +9987,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10037,6 +10149,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-4158.1258082443446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10056,8 +10171,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="560863872"/>
-        <c:axId val="560862336"/>
+        <c:axId val="679028224"/>
+        <c:axId val="679026688"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10082,7 +10197,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10244,6 +10359,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10253,7 +10371,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10415,6 +10533,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10436,11 +10557,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560624384"/>
-        <c:axId val="560626304"/>
+        <c:axId val="676854784"/>
+        <c:axId val="678344960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560624384"/>
+        <c:axId val="676854784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10483,14 +10604,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560626304"/>
+        <c:crossAx val="678344960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560626304"/>
+        <c:axId val="678344960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10541,12 +10662,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560624384"/>
+        <c:crossAx val="676854784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="560862336"/>
+        <c:axId val="679026688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10583,12 +10704,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560863872"/>
+        <c:crossAx val="679028224"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="560863872"/>
+        <c:axId val="679028224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10597,7 +10718,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="560862336"/>
+        <c:crossAx val="679026688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10776,7 +10897,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10938,6 +11059,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10947,7 +11071,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11108,6 +11232,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11151,7 +11278,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11313,6 +11440,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11322,7 +11452,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11484,6 +11614,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>16004082.547668742</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16362949.816239173</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11526,7 +11659,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11688,6 +11821,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11697,7 +11833,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11859,6 +11995,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5116246.7741877642</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5475114.0427581947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11880,11 +12019,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561029504"/>
-        <c:axId val="561031424"/>
+        <c:axId val="679139968"/>
+        <c:axId val="679183488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561029504"/>
+        <c:axId val="679139968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11927,14 +12066,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561031424"/>
+        <c:crossAx val="679183488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561031424"/>
+        <c:axId val="679183488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11985,7 +12124,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561029504"/>
+        <c:crossAx val="679139968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12197,7 +12336,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12359,6 +12498,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-21886.088907832516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12378,8 +12520,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="561346048"/>
-        <c:axId val="561282432"/>
+        <c:axId val="679333248"/>
+        <c:axId val="679331328"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12404,7 +12546,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12566,6 +12708,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12575,7 +12720,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12737,6 +12882,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12758,11 +12906,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561278976"/>
-        <c:axId val="561280896"/>
+        <c:axId val="679328000"/>
+        <c:axId val="679329792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561278976"/>
+        <c:axId val="679328000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12805,14 +12953,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561280896"/>
+        <c:crossAx val="679329792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561280896"/>
+        <c:axId val="679329792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12863,12 +13011,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561278976"/>
+        <c:crossAx val="679328000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="561282432"/>
+        <c:axId val="679331328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12905,12 +13053,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561346048"/>
+        <c:crossAx val="679333248"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="561346048"/>
+        <c:axId val="679333248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12919,7 +13067,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="561282432"/>
+        <c:crossAx val="679331328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13098,7 +13246,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13260,6 +13408,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13269,7 +13420,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13430,6 +13581,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13473,7 +13627,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13635,6 +13789,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13644,7 +13801,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13806,6 +13963,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>2111236.7158821402</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2159110.7382003833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13848,7 +14008,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14010,6 +14170,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14019,7 +14182,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14181,6 +14344,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>792141.12421423499</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>840015.14653247804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14202,11 +14368,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561597440"/>
-        <c:axId val="561648384"/>
+        <c:axId val="680576128"/>
+        <c:axId val="680751488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561597440"/>
+        <c:axId val="680576128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14249,14 +14415,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561648384"/>
+        <c:crossAx val="680751488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561648384"/>
+        <c:axId val="680751488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14307,7 +14473,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561597440"/>
+        <c:crossAx val="680576128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14498,7 +14664,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14660,6 +14826,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-2552.7654460651065</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-1291.963674375447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14679,8 +14848,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="475884160"/>
-        <c:axId val="475882624"/>
+        <c:axId val="682393984"/>
+        <c:axId val="682015360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14705,7 +14874,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14867,6 +15036,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14876,7 +15048,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15038,6 +15210,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15059,11 +15234,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475391872"/>
-        <c:axId val="475393408"/>
+        <c:axId val="681781120"/>
+        <c:axId val="682013440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475391872"/>
+        <c:axId val="681781120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15106,14 +15281,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475393408"/>
+        <c:crossAx val="682013440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475393408"/>
+        <c:axId val="682013440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15164,12 +15339,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475391872"/>
+        <c:crossAx val="681781120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="475882624"/>
+        <c:axId val="682015360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15206,12 +15381,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475884160"/>
+        <c:crossAx val="682393984"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="475884160"/>
+        <c:axId val="682393984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15220,7 +15395,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="475882624"/>
+        <c:crossAx val="682015360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15399,7 +15574,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15561,6 +15736,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15570,7 +15748,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15731,6 +15909,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15774,7 +15955,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15936,6 +16117,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15945,7 +16129,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16107,6 +16291,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1707604.5820033031</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1744929.5685449983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16149,7 +16336,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16311,6 +16498,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16320,7 +16510,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16482,6 +16672,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>532792.78610775061</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570117.7726494458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16503,11 +16696,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="555583360"/>
-        <c:axId val="555584896"/>
+        <c:axId val="543404032"/>
+        <c:axId val="543405568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="555583360"/>
+        <c:axId val="543404032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16550,14 +16743,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555584896"/>
+        <c:crossAx val="543405568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="555584896"/>
+        <c:axId val="543405568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16608,7 +16801,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555583360"/>
+        <c:crossAx val="543404032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17544,7 +17737,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -17675,28 +17868,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -19957,6 +20150,44 @@
       </c>
       <c r="L56" s="29">
         <v>90191.835636928721</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="32">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="31">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="29">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="29">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="30">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="30">
+        <v>1510149.1694970026</v>
+      </c>
+      <c r="H57" s="30">
+        <v>1606798.732186906</v>
+      </c>
+      <c r="I57" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J57" s="30">
+        <v>1717781.1968650564</v>
+      </c>
+      <c r="K57" s="30">
+        <v>559288.16738283262</v>
+      </c>
+      <c r="L57" s="29">
+        <v>110982.46467815044</v>
       </c>
     </row>
   </sheetData>
@@ -19975,7 +20206,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20013,13 +20244,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20046,16 +20277,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20117,28 +20348,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23017,6 +23248,56 @@
       </c>
       <c r="P56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-4158.1258082443446</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-3908.0129391425353</v>
+      </c>
+      <c r="G57" s="18">
+        <v>1744406.8685374688</v>
+      </c>
+      <c r="H57" s="18">
+        <v>1856048.9264234232</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J57" s="18">
+        <v>1934291.8223967806</v>
+      </c>
+      <c r="K57" s="18">
+        <v>614400.23029718734</v>
+      </c>
+      <c r="L57" s="17">
+        <v>78242.895973357343</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -23035,7 +23316,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23073,13 +23354,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23106,16 +23387,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -23177,28 +23458,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26077,6 +26358,56 @@
       </c>
       <c r="P56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-21886.088907832516</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-20569.632229368879</v>
+      </c>
+      <c r="G57" s="18">
+        <v>14932202.922212096</v>
+      </c>
+      <c r="H57" s="18">
+        <v>15887864.065878714</v>
+      </c>
+      <c r="I57" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J57" s="18">
+        <v>16362949.816239173</v>
+      </c>
+      <c r="K57" s="18">
+        <v>5475114.0427581947</v>
+      </c>
+      <c r="L57" s="17">
+        <v>475085.75036045833</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -26095,7 +26426,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26130,22 +26461,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -26166,22 +26497,22 @@
         <v>10</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -26255,28 +26586,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -29473,6 +29804,62 @@
       </c>
       <c r="R56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-1291.963674375447</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-1214.2515616893245</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1993532.6358949887</v>
+      </c>
+      <c r="J57" s="18">
+        <v>2121118.7455052575</v>
+      </c>
+      <c r="K57" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L57" s="18">
+        <v>2159110.7382003833</v>
+      </c>
+      <c r="M57" s="18">
+        <v>840015.14653247804</v>
+      </c>
+      <c r="N57" s="17">
+        <v>37991.992695125584</v>
+      </c>
+      <c r="O57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="P57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="Q57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -29491,7 +29878,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29526,13 +29913,13 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>21</v>
@@ -29562,19 +29949,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -29652,28 +30039,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -32713,6 +33100,59 @@
         <v>83.790672900129579</v>
       </c>
       <c r="Q56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="18">
+        <v>1535664.5561626744</v>
+      </c>
+      <c r="H57" s="18">
+        <v>1633947.1038668479</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J57" s="18">
+        <v>1744929.5685449983</v>
+      </c>
+      <c r="K57" s="18">
+        <v>570117.7726494458</v>
+      </c>
+      <c r="L57" s="17">
+        <v>110982.46467815044</v>
+      </c>
+      <c r="M57" s="21">
+        <v>82.317072210415034</v>
+      </c>
+      <c r="N57" s="21">
+        <v>82.130142596708495</v>
+      </c>
+      <c r="O57" s="21">
+        <v>81.483167688714857</v>
+      </c>
+      <c r="P57" s="21">
+        <v>83.424092412695785</v>
+      </c>
+      <c r="Q57" s="1">
         <v>1</v>
       </c>
     </row>
@@ -32732,7 +33172,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32767,22 +33207,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -32878,28 +33318,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -35478,6 +35918,50 @@
       </c>
       <c r="N56" s="17">
         <v>324719.36588530202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-46393.241034391052</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-43602.669715207558</v>
+      </c>
+      <c r="I57" s="18">
+        <v>12427436.07440454</v>
+      </c>
+      <c r="J57" s="18">
+        <v>13222792.113535423</v>
+      </c>
+      <c r="K57" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L57" s="18">
+        <v>13593904.720455116</v>
+      </c>
+      <c r="M57" s="18">
+        <v>5318264.7271588407</v>
+      </c>
+      <c r="N57" s="17">
+        <v>371112.60691969306</v>
       </c>
     </row>
   </sheetData>
@@ -35496,7 +35980,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35531,7 +36015,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
@@ -35630,25 +36114,25 @@
         <v>1</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -37909,6 +38393,44 @@
       </c>
       <c r="L56" s="17">
         <v>518829.06704185653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="18">
+        <v>12781203.118754858</v>
+      </c>
+      <c r="H57" s="18">
+        <v>13599200.252435327</v>
+      </c>
+      <c r="I57" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J57" s="18">
+        <v>14227459.764016345</v>
+      </c>
+      <c r="K57" s="18">
+        <v>4866124.9462889209</v>
+      </c>
+      <c r="L57" s="17">
+        <v>628259.51158101915</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,6 +145,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,10 +158,6 @@
   </si>
   <si>
     <t>PE均值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -181,15 +177,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>SMA之MAX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>利润</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -671,7 +667,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -836,6 +832,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -845,7 +844,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1009,6 +1008,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1052,7 +1054,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1217,6 +1219,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1226,7 +1231,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1391,6 +1396,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1717781.1968650564</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1729862.4147042707</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,7 +1441,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1598,6 +1606,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1607,7 +1618,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1772,6 +1783,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>559288.16738283262</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>571369.38522204687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1793,11 +1807,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523372416"/>
-        <c:axId val="523411840"/>
+        <c:axId val="90749184"/>
+        <c:axId val="155879296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523372416"/>
+        <c:axId val="90749184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1840,14 +1854,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523411840"/>
+        <c:crossAx val="155879296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523411840"/>
+        <c:axId val="155879296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1898,7 +1912,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523372416"/>
+        <c:crossAx val="90749184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2089,7 +2103,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2254,6 +2268,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,8 +2290,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="565314688"/>
-        <c:axId val="543423872"/>
+        <c:axId val="614376192"/>
+        <c:axId val="614374400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2299,7 +2316,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2464,6 +2481,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2473,7 +2493,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2638,6 +2658,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2659,11 +2682,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543420800"/>
-        <c:axId val="543422336"/>
+        <c:axId val="614371328"/>
+        <c:axId val="614372864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543420800"/>
+        <c:axId val="614371328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2706,14 +2729,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543422336"/>
+        <c:crossAx val="614372864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543422336"/>
+        <c:axId val="614372864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2764,12 +2787,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543420800"/>
+        <c:crossAx val="614371328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="543423872"/>
+        <c:axId val="614374400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,12 +2829,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565314688"/>
+        <c:crossAx val="614376192"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="565314688"/>
+        <c:axId val="614376192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2820,7 +2843,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="543423872"/>
+        <c:crossAx val="614374400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2999,7 +3022,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3164,6 +3187,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3173,7 +3199,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3337,6 +3363,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3380,7 +3409,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3545,6 +3574,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3554,7 +3586,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3719,6 +3751,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>13593904.720455116</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13693324.410529703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3761,7 +3796,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3926,6 +3961,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3935,7 +3973,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4100,6 +4138,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5318264.7271588407</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5417684.417233428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,11 +4162,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565346688"/>
-        <c:axId val="565348224"/>
+        <c:axId val="614957056"/>
+        <c:axId val="614958592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565346688"/>
+        <c:axId val="614957056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4168,14 +4209,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565348224"/>
+        <c:crossAx val="614958592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565348224"/>
+        <c:axId val="614958592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4226,7 +4267,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565346688"/>
+        <c:crossAx val="614957056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4417,7 +4458,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4582,6 +4623,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-46393.241034391052</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-111127.31971233143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4601,8 +4645,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="565372416"/>
-        <c:axId val="565370880"/>
+        <c:axId val="615654528"/>
+        <c:axId val="615652736"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4627,7 +4671,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4792,6 +4836,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4801,7 +4848,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4966,6 +5013,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4987,11 +5037,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565367552"/>
-        <c:axId val="565369088"/>
+        <c:axId val="615649664"/>
+        <c:axId val="615651200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565367552"/>
+        <c:axId val="615649664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5034,14 +5084,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565369088"/>
+        <c:crossAx val="615651200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565369088"/>
+        <c:axId val="615651200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5092,12 +5142,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565367552"/>
+        <c:crossAx val="615649664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="565370880"/>
+        <c:axId val="615652736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5134,12 +5184,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565372416"/>
+        <c:crossAx val="615654528"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="565372416"/>
+        <c:axId val="615654528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5148,7 +5198,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="565370880"/>
+        <c:crossAx val="615652736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5327,7 +5377,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5492,6 +5542,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5501,7 +5554,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5665,6 +5718,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5708,7 +5764,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5873,6 +5929,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5882,7 +5941,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6047,6 +6106,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14227459.764016345</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14329709.596181171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6089,7 +6151,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6254,6 +6316,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6263,7 +6328,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6428,6 +6493,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4866124.9462889209</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4968374.7784537468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6449,11 +6517,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="668537984"/>
-        <c:axId val="668539520"/>
+        <c:axId val="615670144"/>
+        <c:axId val="615671680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="668537984"/>
+        <c:axId val="615670144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6496,14 +6564,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="668539520"/>
+        <c:crossAx val="615671680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="668539520"/>
+        <c:axId val="615671680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6554,7 +6622,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="668537984"/>
+        <c:crossAx val="615670144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6745,7 +6813,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6910,6 +6978,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6929,8 +7000,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="669341952"/>
-        <c:axId val="669340416"/>
+        <c:axId val="615704064"/>
+        <c:axId val="615702528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6955,7 +7026,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7120,6 +7191,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7129,7 +7203,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7294,6 +7368,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7315,11 +7392,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="668562944"/>
-        <c:axId val="668564480"/>
+        <c:axId val="615699200"/>
+        <c:axId val="615700736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="668562944"/>
+        <c:axId val="615699200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7362,14 +7439,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="668564480"/>
+        <c:crossAx val="615700736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="668564480"/>
+        <c:axId val="615700736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7420,12 +7497,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="668562944"/>
+        <c:crossAx val="615699200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="669340416"/>
+        <c:axId val="615702528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7462,12 +7539,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669341952"/>
+        <c:crossAx val="615704064"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="669341952"/>
+        <c:axId val="615704064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7476,7 +7553,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="669340416"/>
+        <c:crossAx val="615702528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7638,7 +7715,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7803,6 +7880,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7822,8 +7902,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="673665792"/>
-        <c:axId val="673639424"/>
+        <c:axId val="564124672"/>
+        <c:axId val="564123136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7848,7 +7928,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8013,6 +8093,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8022,7 +8105,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8187,6 +8270,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8208,11 +8294,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="670297088"/>
-        <c:axId val="673637504"/>
+        <c:axId val="564110464"/>
+        <c:axId val="564112384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="670297088"/>
+        <c:axId val="564110464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8255,14 +8341,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="673637504"/>
+        <c:crossAx val="564112384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="673637504"/>
+        <c:axId val="564112384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8313,12 +8399,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670297088"/>
+        <c:crossAx val="564110464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="673639424"/>
+        <c:axId val="564123136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8355,12 +8441,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="673665792"/>
+        <c:crossAx val="564124672"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="673665792"/>
+        <c:axId val="564124672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8369,7 +8455,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="673639424"/>
+        <c:crossAx val="564123136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8548,7 +8634,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8713,6 +8799,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8722,7 +8811,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8886,6 +8975,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8929,7 +9021,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9094,6 +9186,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9103,7 +9198,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9268,6 +9363,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1934291.8223967806</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1948247.1056262129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9310,7 +9408,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9475,6 +9573,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9484,7 +9585,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9649,6 +9750,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>614400.23029718734</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>628355.51352661964</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9670,11 +9774,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="676790656"/>
-        <c:axId val="676792576"/>
+        <c:axId val="568084736"/>
+        <c:axId val="614359808"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="676790656"/>
+        <c:axId val="568084736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9717,14 +9821,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676792576"/>
+        <c:crossAx val="614359808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="676792576"/>
+        <c:axId val="614359808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9775,7 +9879,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676790656"/>
+        <c:crossAx val="568084736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9987,7 +10091,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10152,6 +10256,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-4158.1258082443446</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-4531.947395988238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10171,8 +10278,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="679028224"/>
-        <c:axId val="679026688"/>
+        <c:axId val="622158208"/>
+        <c:axId val="622156416"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10197,7 +10304,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10362,6 +10469,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10371,7 +10481,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10536,6 +10646,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10557,11 +10670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="676854784"/>
-        <c:axId val="678344960"/>
+        <c:axId val="622152320"/>
+        <c:axId val="622154880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="676854784"/>
+        <c:axId val="622152320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10604,14 +10717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678344960"/>
+        <c:crossAx val="622154880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="678344960"/>
+        <c:axId val="622154880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10662,12 +10775,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676854784"/>
+        <c:crossAx val="622152320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="679026688"/>
+        <c:axId val="622156416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10704,12 +10817,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679028224"/>
+        <c:crossAx val="622158208"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="679028224"/>
+        <c:axId val="622158208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10718,7 +10831,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="679026688"/>
+        <c:crossAx val="622156416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10897,7 +11010,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11062,6 +11175,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11071,7 +11187,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11235,6 +11351,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11278,7 +11397,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11443,6 +11562,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11452,7 +11574,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11617,6 +11739,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>16362949.816239173</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16482407.681704661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11659,7 +11784,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11824,6 +11949,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11833,7 +11961,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11998,6 +12126,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5475114.0427581947</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5594571.908223683</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12019,11 +12150,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="679139968"/>
-        <c:axId val="679183488"/>
+        <c:axId val="622512768"/>
+        <c:axId val="622784896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="679139968"/>
+        <c:axId val="622512768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12066,14 +12197,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679183488"/>
+        <c:crossAx val="622784896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="679183488"/>
+        <c:axId val="622784896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12124,7 +12255,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679139968"/>
+        <c:crossAx val="622512768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12336,7 +12467,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12501,6 +12632,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-21886.088907832516</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-25998.161012664015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12520,8 +12654,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="679333248"/>
-        <c:axId val="679331328"/>
+        <c:axId val="623769856"/>
+        <c:axId val="623768320"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12546,7 +12680,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12711,6 +12845,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12720,7 +12857,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12885,6 +13022,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12906,11 +13046,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="679328000"/>
-        <c:axId val="679329792"/>
+        <c:axId val="623752320"/>
+        <c:axId val="623754240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="679328000"/>
+        <c:axId val="623752320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12953,14 +13093,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679329792"/>
+        <c:crossAx val="623754240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="679329792"/>
+        <c:axId val="623754240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13011,12 +13151,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679328000"/>
+        <c:crossAx val="623752320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="679331328"/>
+        <c:axId val="623768320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13053,12 +13193,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679333248"/>
+        <c:crossAx val="623769856"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="679333248"/>
+        <c:axId val="623769856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13067,7 +13207,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="679331328"/>
+        <c:crossAx val="623768320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13246,7 +13386,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13411,6 +13551,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13420,7 +13563,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13584,6 +13727,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13627,7 +13773,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13792,6 +13938,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13801,7 +13950,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13966,6 +14115,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>2159110.7382003833</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2175059.0316076181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14008,7 +14160,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14173,6 +14325,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14182,7 +14337,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14347,6 +14502,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>840015.14653247804</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>855963.43993971287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14368,11 +14526,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="680576128"/>
-        <c:axId val="680751488"/>
+        <c:axId val="627734784"/>
+        <c:axId val="627901952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="680576128"/>
+        <c:axId val="627734784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14415,14 +14573,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="680751488"/>
+        <c:crossAx val="627901952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="680751488"/>
+        <c:axId val="627901952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14473,7 +14631,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="680576128"/>
+        <c:crossAx val="627734784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14664,7 +14822,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14829,6 +14987,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-1291.963674375447</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-3094.6848527484703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14848,8 +15009,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="682393984"/>
-        <c:axId val="682015360"/>
+        <c:axId val="612012416"/>
+        <c:axId val="611981952"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14874,7 +15035,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15039,6 +15200,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15048,7 +15212,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15213,6 +15377,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15234,11 +15401,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="681781120"/>
-        <c:axId val="682013440"/>
+        <c:axId val="679301120"/>
+        <c:axId val="611980416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="681781120"/>
+        <c:axId val="679301120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15281,14 +15448,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="682013440"/>
+        <c:crossAx val="611980416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="682013440"/>
+        <c:axId val="611980416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15339,12 +15506,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="681781120"/>
+        <c:crossAx val="679301120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="682015360"/>
+        <c:axId val="611981952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15381,12 +15548,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="682393984"/>
+        <c:crossAx val="612012416"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="682393984"/>
+        <c:axId val="612012416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15395,7 +15562,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="682015360"/>
+        <c:crossAx val="611981952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15574,7 +15741,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15739,6 +15906,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15748,7 +15918,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15912,6 +16082,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15955,7 +16128,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16120,6 +16293,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16129,7 +16305,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16294,6 +16470,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1744929.5685449983</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1757214.9098912054</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16336,7 +16515,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16501,6 +16680,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16510,7 +16692,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16675,6 +16857,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>570117.7726494458</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>582403.11399565288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16696,11 +16881,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543404032"/>
-        <c:axId val="543405568"/>
+        <c:axId val="612179328"/>
+        <c:axId val="612185216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543404032"/>
+        <c:axId val="612179328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16743,14 +16928,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543405568"/>
+        <c:crossAx val="612185216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543405568"/>
+        <c:axId val="612185216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16801,7 +16986,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543404032"/>
+        <c:crossAx val="612179328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16902,7 +17087,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16940,7 +17125,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16983,7 +17168,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17021,7 +17206,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17064,7 +17249,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17102,7 +17287,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17145,7 +17330,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17183,7 +17368,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17226,7 +17411,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17264,7 +17449,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17307,7 +17492,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17345,7 +17530,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17388,7 +17573,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17426,7 +17611,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17737,7 +17922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -17868,28 +18053,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20188,6 +20373,44 @@
       </c>
       <c r="L57" s="29">
         <v>110982.46467815044</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="32">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="31">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="29">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="29">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="30">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="30">
+        <v>1489011.355676573</v>
+      </c>
+      <c r="H58" s="30">
+        <v>1596220.2130461792</v>
+      </c>
+      <c r="I58" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J58" s="30">
+        <v>1729862.4147042707</v>
+      </c>
+      <c r="K58" s="30">
+        <v>571369.38522204687</v>
+      </c>
+      <c r="L58" s="29">
+        <v>133642.20165809162</v>
       </c>
     </row>
   </sheetData>
@@ -20206,7 +20429,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20241,10 +20464,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>20</v>
@@ -20277,16 +20500,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="O1" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20348,28 +20571,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23297,6 +23520,56 @@
         <v>77.665854024250493</v>
       </c>
       <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-4531.947395988238</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-4227.5627640859448</v>
+      </c>
+      <c r="G58" s="18">
+        <v>1740179.305773383</v>
+      </c>
+      <c r="H58" s="18">
+        <v>1865472.2622568673</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J58" s="18">
+        <v>1948247.1056262129</v>
+      </c>
+      <c r="K58" s="18">
+        <v>628355.51352661964</v>
+      </c>
+      <c r="L58" s="17">
+        <v>82774.843369345588</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23316,7 +23589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23354,13 +23627,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23387,16 +23660,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="O1" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -23458,28 +23731,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26407,6 +26680,56 @@
         <v>77.665854024250493</v>
       </c>
       <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-25998.161012664015</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-24252.015265919163</v>
+      </c>
+      <c r="G58" s="18">
+        <v>14907950.906946177</v>
+      </c>
+      <c r="H58" s="18">
+        <v>15981323.770331539</v>
+      </c>
+      <c r="I58" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J58" s="18">
+        <v>16482407.681704661</v>
+      </c>
+      <c r="K58" s="18">
+        <v>5594571.908223683</v>
+      </c>
+      <c r="L58" s="17">
+        <v>501083.91137312236</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -26426,7 +26749,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26461,16 +26784,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -26497,22 +26820,22 @@
         <v>10</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="Q1" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="R1" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -26586,28 +26909,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -29859,6 +30182,62 @@
         <v>77.665854024250493</v>
       </c>
       <c r="R57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-3094.6848527484703</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-2886.8328131172739</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1990645.8030818715</v>
+      </c>
+      <c r="J58" s="18">
+        <v>2133972.3540597442</v>
+      </c>
+      <c r="K58" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L58" s="18">
+        <v>2175059.0316076181</v>
+      </c>
+      <c r="M58" s="18">
+        <v>855963.43993971287</v>
+      </c>
+      <c r="N58" s="17">
+        <v>41086.677547874053</v>
+      </c>
+      <c r="O58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="P58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="Q58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="R58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -29878,7 +30257,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29913,16 +30292,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -29949,19 +30328,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="O1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="Q1" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30039,28 +30418,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -33153,6 +33532,59 @@
         <v>83.424092412695785</v>
       </c>
       <c r="Q57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="18">
+        <v>1514526.7423422448</v>
+      </c>
+      <c r="H58" s="18">
+        <v>1623572.7082331136</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J58" s="18">
+        <v>1757214.9098912054</v>
+      </c>
+      <c r="K58" s="18">
+        <v>582403.11399565288</v>
+      </c>
+      <c r="L58" s="17">
+        <v>133642.20165809162</v>
+      </c>
+      <c r="M58" s="21">
+        <v>79.155674275563754</v>
+      </c>
+      <c r="N58" s="21">
+        <v>81.138653156326924</v>
+      </c>
+      <c r="O58" s="21">
+        <v>81.368329511252213</v>
+      </c>
+      <c r="P58" s="21">
+        <v>80.679300446476333</v>
+      </c>
+      <c r="Q58" s="1">
         <v>1</v>
       </c>
     </row>
@@ -33172,7 +33604,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33207,16 +33639,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -33318,28 +33750,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -35962,6 +36394,50 @@
       </c>
       <c r="N57" s="17">
         <v>371112.60691969306</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-111127.31971233143</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-103663.54192557483</v>
+      </c>
+      <c r="I58" s="18">
+        <v>12323772.532478964</v>
+      </c>
+      <c r="J58" s="18">
+        <v>13211084.483897679</v>
+      </c>
+      <c r="K58" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L58" s="18">
+        <v>13693324.410529703</v>
+      </c>
+      <c r="M58" s="18">
+        <v>5417684.417233428</v>
+      </c>
+      <c r="N58" s="17">
+        <v>482239.92663202446</v>
       </c>
     </row>
   </sheetData>
@@ -35980,7 +36456,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36015,7 +36491,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
@@ -36114,25 +36590,25 @@
         <v>1</v>
       </c>
       <c r="Q3" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -38431,6 +38907,44 @@
       </c>
       <c r="L57" s="17">
         <v>628259.51158101915</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="18">
+        <v>12659943.042425262</v>
+      </c>
+      <c r="H58" s="18">
+        <v>13571459.279536832</v>
+      </c>
+      <c r="I58" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J58" s="18">
+        <v>14329709.596181171</v>
+      </c>
+      <c r="K58" s="18">
+        <v>4968374.7784537468</v>
+      </c>
+      <c r="L58" s="17">
+        <v>758250.31664433924</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -145,19 +149,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PE均值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -174,10 +174,6 @@
   </si>
   <si>
     <t>标志</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMA之MAX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -667,7 +663,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -835,6 +831,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,7 +843,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1011,6 +1010,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1054,7 +1056,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1222,6 +1224,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1231,7 +1236,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1399,6 +1404,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1729862.4147042707</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1734329.4800120019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1441,7 +1449,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1609,6 +1617,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1618,7 +1629,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1786,6 +1797,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>571369.38522204687</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>575836.45052977814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1807,11 +1821,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90749184"/>
-        <c:axId val="155879296"/>
+        <c:axId val="531461248"/>
+        <c:axId val="531489920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90749184"/>
+        <c:axId val="531461248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1854,14 +1868,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155879296"/>
+        <c:crossAx val="531489920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="155879296"/>
+        <c:axId val="531489920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1912,7 +1926,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90749184"/>
+        <c:crossAx val="531461248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2103,7 +2117,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2271,6 +2285,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2290,8 +2307,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="614376192"/>
-        <c:axId val="614374400"/>
+        <c:axId val="511820544"/>
+        <c:axId val="511802368"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2316,7 +2333,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2484,6 +2501,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2493,7 +2513,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2661,6 +2681,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2682,11 +2705,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614371328"/>
-        <c:axId val="614372864"/>
+        <c:axId val="511799296"/>
+        <c:axId val="511800832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614371328"/>
+        <c:axId val="511799296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2729,14 +2752,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614372864"/>
+        <c:crossAx val="511800832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614372864"/>
+        <c:axId val="511800832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2787,12 +2810,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614371328"/>
+        <c:crossAx val="511799296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="614374400"/>
+        <c:axId val="511802368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2829,12 +2852,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614376192"/>
+        <c:crossAx val="511820544"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="614376192"/>
+        <c:axId val="511820544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2843,7 +2866,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614374400"/>
+        <c:crossAx val="511802368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3022,7 +3045,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3190,6 +3213,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3199,7 +3225,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3366,6 +3392,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3409,7 +3438,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3577,6 +3606,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3586,7 +3618,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3754,6 +3786,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>13693324.410529703</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>13730295.986690177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3796,7 +3831,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3964,6 +3999,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3973,7 +4011,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4141,6 +4179,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5417684.417233428</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5454655.9933939017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4162,11 +4203,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614957056"/>
-        <c:axId val="614958592"/>
+        <c:axId val="512155648"/>
+        <c:axId val="512157184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614957056"/>
+        <c:axId val="512155648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4209,14 +4250,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614958592"/>
+        <c:crossAx val="512157184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614958592"/>
+        <c:axId val="512157184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4267,7 +4308,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614957056"/>
+        <c:crossAx val="512155648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4458,7 +4499,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4626,6 +4667,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-111127.31971233143</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-56932.913434554059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4645,8 +4689,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="615654528"/>
-        <c:axId val="615652736"/>
+        <c:axId val="523043968"/>
+        <c:axId val="522935680"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4671,7 +4715,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4839,6 +4883,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4895,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5016,6 +5063,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5037,11 +5087,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615649664"/>
-        <c:axId val="615651200"/>
+        <c:axId val="522932608"/>
+        <c:axId val="522934144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615649664"/>
+        <c:axId val="522932608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5084,14 +5134,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615651200"/>
+        <c:crossAx val="522934144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615651200"/>
+        <c:axId val="522934144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5142,12 +5192,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615649664"/>
+        <c:crossAx val="522932608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="615652736"/>
+        <c:axId val="522935680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5184,12 +5234,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615654528"/>
+        <c:crossAx val="523043968"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="615654528"/>
+        <c:axId val="523043968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5198,7 +5248,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="615652736"/>
+        <c:crossAx val="522935680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5377,7 +5427,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5545,6 +5595,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5554,7 +5607,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5721,6 +5774,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5764,7 +5820,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5932,6 +5988,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5941,7 +6000,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6109,6 +6168,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14329709.596181171</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14367689.690924622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6151,7 +6213,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6319,6 +6381,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6328,7 +6393,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6496,6 +6561,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4968374.7784537468</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5006354.8731971979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6517,11 +6585,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615670144"/>
-        <c:axId val="615671680"/>
+        <c:axId val="523063680"/>
+        <c:axId val="523065216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615670144"/>
+        <c:axId val="523063680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6564,14 +6632,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615671680"/>
+        <c:crossAx val="523065216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615671680"/>
+        <c:axId val="523065216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6622,7 +6690,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615670144"/>
+        <c:crossAx val="523063680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6813,7 +6881,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6981,6 +7049,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7000,8 +7071,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="615704064"/>
-        <c:axId val="615702528"/>
+        <c:axId val="523408896"/>
+        <c:axId val="523407360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7026,7 +7097,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7194,6 +7265,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7203,7 +7277,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7371,6 +7445,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7392,11 +7469,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615699200"/>
-        <c:axId val="615700736"/>
+        <c:axId val="523399936"/>
+        <c:axId val="523401472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615699200"/>
+        <c:axId val="523399936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7439,14 +7516,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615700736"/>
+        <c:crossAx val="523401472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615700736"/>
+        <c:axId val="523401472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7497,12 +7574,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615699200"/>
+        <c:crossAx val="523399936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="615702528"/>
+        <c:axId val="523407360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7539,12 +7616,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615704064"/>
+        <c:crossAx val="523408896"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="615704064"/>
+        <c:axId val="523408896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7553,7 +7630,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="615702528"/>
+        <c:crossAx val="523407360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7715,7 +7792,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7883,6 +7960,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7902,8 +7982,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="564124672"/>
-        <c:axId val="564123136"/>
+        <c:axId val="538417792"/>
+        <c:axId val="538415872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7928,7 +8008,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8096,6 +8176,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8105,7 +8188,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8273,6 +8356,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8294,11 +8380,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="564110464"/>
-        <c:axId val="564112384"/>
+        <c:axId val="538392064"/>
+        <c:axId val="538393600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="564110464"/>
+        <c:axId val="538392064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8341,14 +8427,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564112384"/>
+        <c:crossAx val="538393600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="564112384"/>
+        <c:axId val="538393600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8399,12 +8485,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564110464"/>
+        <c:crossAx val="538392064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="564123136"/>
+        <c:axId val="538415872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8441,12 +8527,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564124672"/>
+        <c:crossAx val="538417792"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="564124672"/>
+        <c:axId val="538417792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8455,7 +8541,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="564123136"/>
+        <c:crossAx val="538415872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8634,7 +8720,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8802,6 +8888,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8811,7 +8900,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8978,6 +9067,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9021,7 +9113,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9189,6 +9281,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9198,7 +9293,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9366,6 +9461,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1948247.1056262129</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1953467.680053948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9408,7 +9506,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9576,6 +9674,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9585,7 +9686,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9753,6 +9854,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>628355.51352661964</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>633576.08795435471</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9774,11 +9878,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568084736"/>
-        <c:axId val="614359808"/>
+        <c:axId val="540246400"/>
+        <c:axId val="540248320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568084736"/>
+        <c:axId val="540246400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9821,14 +9925,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614359808"/>
+        <c:crossAx val="540248320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614359808"/>
+        <c:axId val="540248320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9879,7 +9983,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568084736"/>
+        <c:crossAx val="540246400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10091,7 +10195,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10259,6 +10363,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-4531.947395988238</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-4353.0431608345843</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10278,8 +10385,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="622158208"/>
-        <c:axId val="622156416"/>
+        <c:axId val="541197824"/>
+        <c:axId val="541097344"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10304,7 +10411,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10472,6 +10579,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10481,7 +10591,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10649,6 +10759,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10670,11 +10783,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622152320"/>
-        <c:axId val="622154880"/>
+        <c:axId val="541093888"/>
+        <c:axId val="541095424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622152320"/>
+        <c:axId val="541093888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10717,14 +10830,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622154880"/>
+        <c:crossAx val="541095424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="622154880"/>
+        <c:axId val="541095424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10775,12 +10888,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622152320"/>
+        <c:crossAx val="541093888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="622156416"/>
+        <c:axId val="541097344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10817,12 +10930,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622158208"/>
+        <c:crossAx val="541197824"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="622158208"/>
+        <c:axId val="541197824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10831,7 +10944,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="622156416"/>
+        <c:crossAx val="541097344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11010,7 +11123,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11178,6 +11291,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11187,7 +11303,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11354,6 +11470,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11397,7 +11516,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11565,6 +11684,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11574,7 +11696,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11742,6 +11864,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>16482407.681704661</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16527131.847206756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11784,7 +11909,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11952,6 +12077,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11961,7 +12089,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12129,6 +12257,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5594571.908223683</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5639296.0737257786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12150,11 +12281,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622512768"/>
-        <c:axId val="622784896"/>
+        <c:axId val="541342336"/>
+        <c:axId val="541439104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622512768"/>
+        <c:axId val="541342336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12197,14 +12328,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622784896"/>
+        <c:crossAx val="541439104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="622784896"/>
+        <c:axId val="541439104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12255,7 +12386,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622512768"/>
+        <c:crossAx val="541342336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12467,7 +12598,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12635,6 +12766,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-25998.161012664015</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-23986.056658340185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12654,8 +12788,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="623769856"/>
-        <c:axId val="623768320"/>
+        <c:axId val="431640576"/>
+        <c:axId val="431638784"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12680,7 +12814,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12848,6 +12982,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12857,7 +12994,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13025,6 +13162,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13046,11 +13186,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623752320"/>
-        <c:axId val="623754240"/>
+        <c:axId val="431635456"/>
+        <c:axId val="431637248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623752320"/>
+        <c:axId val="431635456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13093,14 +13233,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623754240"/>
+        <c:crossAx val="431637248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623754240"/>
+        <c:axId val="431637248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13151,12 +13291,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623752320"/>
+        <c:crossAx val="431635456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="623768320"/>
+        <c:axId val="431638784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13193,12 +13333,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623769856"/>
+        <c:crossAx val="431640576"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="623769856"/>
+        <c:axId val="431640576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13207,7 +13347,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="623768320"/>
+        <c:crossAx val="431638784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13386,7 +13526,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13554,6 +13694,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13563,7 +13706,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13730,6 +13873,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13773,7 +13919,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13941,6 +14087,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13950,7 +14099,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14118,6 +14267,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>2175059.0316076181</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2181031.0107822744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14160,7 +14312,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14328,6 +14480,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14337,7 +14492,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14505,6 +14660,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>855963.43993971287</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>861935.4191143692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14526,11 +14684,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="627734784"/>
-        <c:axId val="627901952"/>
+        <c:axId val="448412672"/>
+        <c:axId val="448434944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="627734784"/>
+        <c:axId val="448412672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14573,14 +14731,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="627901952"/>
+        <c:crossAx val="448434944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="627901952"/>
+        <c:axId val="448434944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14631,7 +14789,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="627734784"/>
+        <c:crossAx val="448412672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14822,7 +14980,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14990,6 +15148,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-3094.6848527484703</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-1585.4735386837842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15009,8 +15170,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="612012416"/>
-        <c:axId val="611981952"/>
+        <c:axId val="448455040"/>
+        <c:axId val="448453248"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15035,7 +15196,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15203,6 +15364,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15212,7 +15376,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15380,6 +15544,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15401,11 +15568,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="679301120"/>
-        <c:axId val="611980416"/>
+        <c:axId val="448449920"/>
+        <c:axId val="448451712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="679301120"/>
+        <c:axId val="448449920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15448,14 +15615,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611980416"/>
+        <c:crossAx val="448451712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="611980416"/>
+        <c:axId val="448451712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15506,12 +15673,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679301120"/>
+        <c:crossAx val="448449920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="611981952"/>
+        <c:axId val="448453248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15548,12 +15715,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612012416"/>
+        <c:crossAx val="448455040"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="612012416"/>
+        <c:axId val="448455040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15562,7 +15729,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="611981952"/>
+        <c:crossAx val="448453248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15741,7 +15908,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15909,6 +16076,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15918,7 +16088,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16085,6 +16255,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16128,7 +16301,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16296,6 +16469,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16305,7 +16481,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16473,6 +16649,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1757214.9098912054</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1761758.5218942678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16515,7 +16694,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16683,6 +16862,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16692,7 +16874,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16860,6 +17042,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>582403.11399565288</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>586946.72599871526</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16881,11 +17066,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="612179328"/>
-        <c:axId val="612185216"/>
+        <c:axId val="511774080"/>
+        <c:axId val="511775872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="612179328"/>
+        <c:axId val="511774080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16928,14 +17113,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612185216"/>
+        <c:crossAx val="511775872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="612185216"/>
+        <c:axId val="511775872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16986,7 +17171,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612179328"/>
+        <c:crossAx val="511774080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17922,7 +18107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18053,28 +18238,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20411,6 +20596,44 @@
       </c>
       <c r="L58" s="29">
         <v>133642.20165809162</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="32">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="29">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="29">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="30">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="30">
+        <v>1468764.6441986805</v>
+      </c>
+      <c r="H59" s="30">
+        <v>1578922.0625497375</v>
+      </c>
+      <c r="I59" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J59" s="30">
+        <v>1734329.4800120019</v>
+      </c>
+      <c r="K59" s="30">
+        <v>575836.45052977814</v>
+      </c>
+      <c r="L59" s="29">
+        <v>155407.41746226454</v>
       </c>
     </row>
   </sheetData>
@@ -20429,7 +20652,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20464,16 +20687,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20571,28 +20794,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23570,6 +23793,56 @@
         <v>78.476878875019352</v>
       </c>
       <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-4353.0431608345843</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-4049.342295578509</v>
+      </c>
+      <c r="G59" s="18">
+        <v>1736129.9634778046</v>
+      </c>
+      <c r="H59" s="18">
+        <v>1866339.7935237677</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J59" s="18">
+        <v>1953467.680053948</v>
+      </c>
+      <c r="K59" s="18">
+        <v>633576.08795435471</v>
+      </c>
+      <c r="L59" s="17">
+        <v>87127.886530180171</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23589,7 +23862,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23630,10 +23903,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23660,7 +23933,7 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>23</v>
@@ -23731,28 +24004,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26730,6 +27003,56 @@
         <v>78.476878875019352</v>
       </c>
       <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-23986.056658340185</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-22312.609855248407</v>
+      </c>
+      <c r="G59" s="18">
+        <v>14885638.297090929</v>
+      </c>
+      <c r="H59" s="18">
+        <v>16002061.879175294</v>
+      </c>
+      <c r="I59" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J59" s="18">
+        <v>16527131.847206756</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5639296.0737257786</v>
+      </c>
+      <c r="L59" s="17">
+        <v>525069.96803146251</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -26749,7 +27072,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26784,22 +27107,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -26826,7 +27149,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P1" s="44" t="s">
         <v>23</v>
@@ -26909,28 +27232,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30238,6 +30561,62 @@
         <v>78.476878875019352</v>
       </c>
       <c r="R58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-1585.4735386837842</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-1474.8590403321161</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1989170.9440415394</v>
+      </c>
+      <c r="J59" s="18">
+        <v>2138358.8596957168</v>
+      </c>
+      <c r="K59" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L59" s="18">
+        <v>2181031.0107822744</v>
+      </c>
+      <c r="M59" s="18">
+        <v>861935.4191143692</v>
+      </c>
+      <c r="N59" s="17">
+        <v>42672.151086557838</v>
+      </c>
+      <c r="O59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="P59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="Q59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="R59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -30257,7 +30636,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30292,16 +30671,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -30328,19 +30707,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="O1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="Q1" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30418,28 +30797,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -33585,6 +33964,59 @@
         <v>80.679300446476333</v>
       </c>
       <c r="Q58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="18">
+        <v>1494280.0308643524</v>
+      </c>
+      <c r="H59" s="18">
+        <v>1606351.1044320031</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J59" s="18">
+        <v>1761758.5218942678</v>
+      </c>
+      <c r="K59" s="18">
+        <v>586946.72599871526</v>
+      </c>
+      <c r="L59" s="17">
+        <v>155407.41746226454</v>
+      </c>
+      <c r="M59" s="21">
+        <v>79.947236522705992</v>
+      </c>
+      <c r="N59" s="21">
+        <v>80.74151427845328</v>
+      </c>
+      <c r="O59" s="21">
+        <v>81.15939110031924</v>
+      </c>
+      <c r="P59" s="21">
+        <v>79.905760634721361</v>
+      </c>
+      <c r="Q59" s="1">
         <v>1</v>
       </c>
     </row>
@@ -33604,7 +34036,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33639,22 +34071,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -33750,28 +34182,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36438,6 +36870,50 @@
       </c>
       <c r="N58" s="17">
         <v>482239.92663202446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-56932.913434554059</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-52960.847357380524</v>
+      </c>
+      <c r="I59" s="18">
+        <v>12270811.685121583</v>
+      </c>
+      <c r="J59" s="18">
+        <v>13191123.146623598</v>
+      </c>
+      <c r="K59" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L59" s="18">
+        <v>13730295.986690177</v>
+      </c>
+      <c r="M59" s="18">
+        <v>5454655.9933939017</v>
+      </c>
+      <c r="N59" s="17">
+        <v>539172.84006657847</v>
       </c>
     </row>
   </sheetData>
@@ -36456,7 +36932,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36491,16 +36967,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -36587,28 +37063,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -38945,6 +39421,44 @@
       </c>
       <c r="L58" s="17">
         <v>758250.31664433924</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="18">
+        <v>12548379.99314902</v>
+      </c>
+      <c r="H59" s="18">
+        <v>13489509.090988582</v>
+      </c>
+      <c r="I59" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J59" s="18">
+        <v>14367689.690924622</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5006354.8731971979</v>
+      </c>
+      <c r="L59" s="17">
+        <v>878180.59993604012</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="29">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -146,18 +142,6 @@
   </si>
   <si>
     <t>年化收益率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -663,7 +647,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -834,6 +818,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -843,7 +830,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1013,6 +1000,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1056,7 +1046,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1227,6 +1217,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1236,7 +1229,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1407,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1734329.4800120019</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1694672.7323658499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1449,7 +1445,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1620,6 +1616,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1629,7 +1628,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1800,6 +1799,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>575836.45052977814</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>536179.7028836261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1821,11 +1823,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="531461248"/>
-        <c:axId val="531489920"/>
+        <c:axId val="528543104"/>
+        <c:axId val="529729792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="531461248"/>
+        <c:axId val="528543104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1868,14 +1870,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531489920"/>
+        <c:crossAx val="529729792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="531489920"/>
+        <c:axId val="529729792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1926,7 +1928,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531461248"/>
+        <c:crossAx val="528543104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2117,7 +2119,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2288,6 +2290,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2307,8 +2312,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="511820544"/>
-        <c:axId val="511802368"/>
+        <c:axId val="526537856"/>
+        <c:axId val="526531968"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2333,7 +2338,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2504,6 +2509,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2513,7 +2521,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2684,6 +2692,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2705,11 +2716,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511799296"/>
-        <c:axId val="511800832"/>
+        <c:axId val="526528896"/>
+        <c:axId val="526530432"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511799296"/>
+        <c:axId val="526528896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,14 +2763,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511800832"/>
+        <c:crossAx val="526530432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511800832"/>
+        <c:axId val="526530432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2810,12 +2821,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511799296"/>
+        <c:crossAx val="526528896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="511802368"/>
+        <c:axId val="526531968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2852,12 +2863,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511820544"/>
+        <c:crossAx val="526537856"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="511820544"/>
+        <c:axId val="526537856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2866,7 +2877,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="511802368"/>
+        <c:crossAx val="526531968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3045,7 +3056,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3216,6 +3227,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3225,7 +3239,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3395,6 +3409,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3438,7 +3455,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3609,6 +3626,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3618,7 +3638,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3789,6 +3809,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>13730295.986690177</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13398983.216919765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3831,7 +3854,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4002,6 +4025,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4011,7 +4037,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4182,6 +4208,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5454655.9933939017</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5123343.22362349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,11 +4232,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="512155648"/>
-        <c:axId val="512157184"/>
+        <c:axId val="526561664"/>
+        <c:axId val="526563200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="512155648"/>
+        <c:axId val="526561664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4250,14 +4279,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="512157184"/>
+        <c:crossAx val="526563200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="512157184"/>
+        <c:axId val="526563200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4308,7 +4337,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="512155648"/>
+        <c:crossAx val="526561664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4499,7 +4528,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4670,6 +4699,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-56932.913434554059</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-37743.814809844756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4689,8 +4721,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="523043968"/>
-        <c:axId val="522935680"/>
+        <c:axId val="527062528"/>
+        <c:axId val="527060992"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4715,7 +4747,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4886,6 +4918,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4895,7 +4930,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5066,6 +5101,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5087,11 +5125,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522932608"/>
-        <c:axId val="522934144"/>
+        <c:axId val="527053568"/>
+        <c:axId val="527055104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522932608"/>
+        <c:axId val="527053568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5134,14 +5172,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522934144"/>
+        <c:crossAx val="527055104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522934144"/>
+        <c:axId val="527055104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5192,12 +5230,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522932608"/>
+        <c:crossAx val="527053568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522935680"/>
+        <c:axId val="527060992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5234,12 +5272,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523043968"/>
+        <c:crossAx val="527062528"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="523043968"/>
+        <c:axId val="527062528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5248,7 +5286,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522935680"/>
+        <c:crossAx val="527060992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5427,7 +5465,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5598,6 +5636,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5607,7 +5648,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5777,6 +5818,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5820,7 +5864,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5991,6 +6035,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6000,7 +6047,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6171,6 +6218,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14367689.690924622</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14028882.557513656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6213,7 +6263,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6384,6 +6434,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6393,7 +6446,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6564,6 +6617,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5006354.8731971979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4667547.7397862319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6585,11 +6641,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523063680"/>
-        <c:axId val="523065216"/>
+        <c:axId val="528098048"/>
+        <c:axId val="528099584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523063680"/>
+        <c:axId val="528098048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6632,14 +6688,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523065216"/>
+        <c:crossAx val="528099584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523065216"/>
+        <c:axId val="528099584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6690,7 +6746,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523063680"/>
+        <c:crossAx val="528098048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6881,7 +6937,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7052,6 +7108,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7071,8 +7130,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="523408896"/>
-        <c:axId val="523407360"/>
+        <c:axId val="528484224"/>
+        <c:axId val="528482688"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7097,7 +7156,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7268,6 +7327,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7277,7 +7339,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7448,6 +7510,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7469,11 +7534,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523399936"/>
-        <c:axId val="523401472"/>
+        <c:axId val="528151680"/>
+        <c:axId val="528153216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523399936"/>
+        <c:axId val="528151680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7516,14 +7581,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523401472"/>
+        <c:crossAx val="528153216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523401472"/>
+        <c:axId val="528153216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7574,12 +7639,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523399936"/>
+        <c:crossAx val="528151680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="523407360"/>
+        <c:axId val="528482688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7616,12 +7681,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523408896"/>
+        <c:crossAx val="528484224"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="523408896"/>
+        <c:axId val="528484224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7630,7 +7695,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="523407360"/>
+        <c:crossAx val="528482688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7792,7 +7857,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7963,6 +8028,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7982,8 +8050,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="538417792"/>
-        <c:axId val="538415872"/>
+        <c:axId val="534055552"/>
+        <c:axId val="534054016"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8008,7 +8076,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8179,6 +8247,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8188,7 +8259,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8359,6 +8430,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8380,11 +8454,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538392064"/>
-        <c:axId val="538393600"/>
+        <c:axId val="534049152"/>
+        <c:axId val="534051840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538392064"/>
+        <c:axId val="534049152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8427,14 +8501,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538393600"/>
+        <c:crossAx val="534051840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538393600"/>
+        <c:axId val="534051840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8485,12 +8559,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538392064"/>
+        <c:crossAx val="534049152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="538415872"/>
+        <c:axId val="534054016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8527,12 +8601,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538417792"/>
+        <c:crossAx val="534055552"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="538417792"/>
+        <c:axId val="534055552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8541,7 +8615,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="538415872"/>
+        <c:crossAx val="534054016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8720,7 +8794,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8891,6 +8965,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8900,7 +8977,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9070,6 +9147,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9113,7 +9193,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9284,6 +9364,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9293,7 +9376,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9464,6 +9547,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1953467.680053948</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1906592.0501737606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9506,7 +9592,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9677,6 +9763,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9686,7 +9775,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9857,6 +9946,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>633576.08795435471</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>586700.45807416737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9878,11 +9970,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="540246400"/>
-        <c:axId val="540248320"/>
+        <c:axId val="534128128"/>
+        <c:axId val="534138880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="540246400"/>
+        <c:axId val="534128128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9925,14 +10017,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540248320"/>
+        <c:crossAx val="534138880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="540248320"/>
+        <c:axId val="534138880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9983,7 +10075,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540246400"/>
+        <c:crossAx val="534128128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10195,7 +10287,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10366,6 +10458,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-4353.0431608345843</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-3486.2836718054768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10385,8 +10480,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="541197824"/>
-        <c:axId val="541097344"/>
+        <c:axId val="535066112"/>
+        <c:axId val="535055744"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10411,7 +10506,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10582,6 +10677,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10591,7 +10689,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10762,6 +10860,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10783,11 +10884,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="541093888"/>
-        <c:axId val="541095424"/>
+        <c:axId val="534854656"/>
+        <c:axId val="535053056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="541093888"/>
+        <c:axId val="534854656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10830,14 +10931,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541095424"/>
+        <c:crossAx val="535053056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="541095424"/>
+        <c:axId val="535053056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10888,12 +10989,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541093888"/>
+        <c:crossAx val="534854656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="541097344"/>
+        <c:axId val="535055744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10930,12 +11031,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541197824"/>
+        <c:crossAx val="535066112"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="541197824"/>
+        <c:axId val="535066112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10944,7 +11045,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="541097344"/>
+        <c:crossAx val="535055744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11123,7 +11224,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11294,6 +11395,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11303,7 +11407,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11473,6 +11577,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11516,7 +11623,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11687,6 +11794,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11696,7 +11806,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11867,6 +11977,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>16527131.847206756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16125218.576873584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11909,7 +12022,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12080,6 +12193,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12089,7 +12205,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12260,6 +12376,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5639296.0737257786</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5237382.8033926059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12281,11 +12400,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="541342336"/>
-        <c:axId val="541439104"/>
+        <c:axId val="535366272"/>
+        <c:axId val="535404928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="541342336"/>
+        <c:axId val="535366272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12328,14 +12447,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541439104"/>
+        <c:crossAx val="535404928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="541439104"/>
+        <c:axId val="535404928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12386,7 +12505,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541342336"/>
+        <c:crossAx val="535366272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12598,7 +12717,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12769,6 +12888,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-23986.056658340185</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-15385.030177591741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12788,8 +12910,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="431640576"/>
-        <c:axId val="431638784"/>
+        <c:axId val="535681664"/>
+        <c:axId val="535680128"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12814,7 +12936,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12985,6 +13107,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12994,7 +13119,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13165,6 +13290,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13186,11 +13314,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="431635456"/>
-        <c:axId val="431637248"/>
+        <c:axId val="535532672"/>
+        <c:axId val="535534976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="431635456"/>
+        <c:axId val="535532672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13233,14 +13361,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431637248"/>
+        <c:crossAx val="535534976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="431637248"/>
+        <c:axId val="535534976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13291,12 +13419,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431635456"/>
+        <c:crossAx val="535532672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="431638784"/>
+        <c:axId val="535680128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13333,12 +13461,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431640576"/>
+        <c:crossAx val="535681664"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="431640576"/>
+        <c:axId val="535681664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13347,7 +13475,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="431638784"/>
+        <c:crossAx val="535680128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13526,7 +13654,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13697,6 +13825,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13706,7 +13837,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13876,6 +14007,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13919,7 +14053,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14090,6 +14224,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14099,7 +14236,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14270,6 +14407,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>2181031.0107822744</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2127323.2568106027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14312,7 +14452,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14483,6 +14623,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14492,7 +14635,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14663,6 +14806,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>861935.4191143692</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>808227.66514269751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14684,11 +14830,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448412672"/>
-        <c:axId val="448434944"/>
+        <c:axId val="536128896"/>
+        <c:axId val="536196608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448412672"/>
+        <c:axId val="536128896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14731,14 +14877,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448434944"/>
+        <c:crossAx val="536196608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448434944"/>
+        <c:axId val="536196608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14789,7 +14935,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448412672"/>
+        <c:crossAx val="536128896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14980,7 +15126,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15151,6 +15297,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-1585.4735386837842</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-1051.0935769830185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15170,8 +15319,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="448455040"/>
-        <c:axId val="448453248"/>
+        <c:axId val="526226176"/>
+        <c:axId val="526220288"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15196,7 +15345,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15367,6 +15516,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15376,7 +15528,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15547,6 +15699,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15568,11 +15723,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448449920"/>
-        <c:axId val="448451712"/>
+        <c:axId val="526217216"/>
+        <c:axId val="526218752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448449920"/>
+        <c:axId val="526217216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15615,14 +15770,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448451712"/>
+        <c:crossAx val="526218752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448451712"/>
+        <c:axId val="526218752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15673,12 +15828,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448449920"/>
+        <c:crossAx val="526217216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="448453248"/>
+        <c:axId val="526220288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15715,12 +15870,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448455040"/>
+        <c:crossAx val="526226176"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="448455040"/>
+        <c:axId val="526226176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15729,7 +15884,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="448453248"/>
+        <c:crossAx val="526220288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15908,7 +16063,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16079,6 +16234,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16088,7 +16246,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16258,6 +16416,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16301,7 +16462,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16472,6 +16633,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16481,7 +16645,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16652,6 +16816,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1761758.5218942678</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1721412.8570318066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16694,7 +16861,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16865,6 +17032,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16874,7 +17044,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17045,6 +17215,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>586946.72599871526</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>546601.06113625411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17066,11 +17239,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511774080"/>
-        <c:axId val="511775872"/>
+        <c:axId val="526495744"/>
+        <c:axId val="526497280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511774080"/>
+        <c:axId val="526495744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17113,14 +17286,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511775872"/>
+        <c:crossAx val="526497280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511775872"/>
+        <c:axId val="526497280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17171,7 +17344,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511774080"/>
+        <c:crossAx val="526495744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18107,7 +18280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18238,28 +18411,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20634,6 +20807,44 @@
       </c>
       <c r="L59" s="29">
         <v>155407.41746226454</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="32">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="29">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="29">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="30">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="30">
+        <v>1452131.6110652217</v>
+      </c>
+      <c r="H60" s="30">
+        <v>1521833.896544558</v>
+      </c>
+      <c r="I60" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J60" s="30">
+        <v>1694672.7323658499</v>
+      </c>
+      <c r="K60" s="30">
+        <v>536179.7028836261</v>
+      </c>
+      <c r="L60" s="29">
+        <v>172838.83582129193</v>
       </c>
     </row>
   </sheetData>
@@ -20652,7 +20863,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20687,16 +20898,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20723,16 +20934,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20794,28 +21005,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23843,6 +24054,56 @@
         <v>78.82293398981966</v>
       </c>
       <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-3486.2836718054768</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-3326.6066266917564</v>
+      </c>
+      <c r="G60" s="18">
+        <v>1732803.3568511128</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1815977.879971775</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J60" s="18">
+        <v>1906592.0501737606</v>
+      </c>
+      <c r="K60" s="18">
+        <v>586700.45807416737</v>
+      </c>
+      <c r="L60" s="17">
+        <v>90614.170201985646</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23862,7 +24123,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23903,10 +24164,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23933,16 +24194,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24004,28 +24265,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27053,6 +27314,56 @@
         <v>78.82293398981966</v>
       </c>
       <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-15385.030177591741</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-14680.372614120717</v>
+      </c>
+      <c r="G60" s="18">
+        <v>14870957.924476808</v>
+      </c>
+      <c r="H60" s="18">
+        <v>15584763.57866453</v>
+      </c>
+      <c r="I60" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J60" s="18">
+        <v>16125218.576873584</v>
+      </c>
+      <c r="K60" s="18">
+        <v>5237382.8033926059</v>
+      </c>
+      <c r="L60" s="17">
+        <v>540454.99820905423</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -27072,7 +27383,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27107,22 +27418,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27149,16 +27460,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -27232,28 +27543,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30617,6 +30928,62 @@
         <v>78.82293398981966</v>
       </c>
       <c r="R59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-1051.0935769830185</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-1002.9519074258362</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1988167.9921341136</v>
+      </c>
+      <c r="J60" s="18">
+        <v>2083600.0121470618</v>
+      </c>
+      <c r="K60" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L60" s="18">
+        <v>2127323.2568106027</v>
+      </c>
+      <c r="M60" s="18">
+        <v>808227.66514269751</v>
+      </c>
+      <c r="N60" s="17">
+        <v>43723.244663540856</v>
+      </c>
+      <c r="O60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="P60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="Q60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="R60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -30636,7 +31003,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30671,16 +31038,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -30707,19 +31074,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="N1" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30797,28 +31164,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34017,6 +34384,59 @@
         <v>79.905760634721361</v>
       </c>
       <c r="Q59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="18">
+        <v>1477646.9977308935</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1548574.0212105147</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J60" s="18">
+        <v>1721412.8570318066</v>
+      </c>
+      <c r="K60" s="18">
+        <v>546601.06113625411</v>
+      </c>
+      <c r="L60" s="17">
+        <v>172838.83582129193</v>
+      </c>
+      <c r="M60" s="21">
+        <v>70.655258802170835</v>
+      </c>
+      <c r="N60" s="21">
+        <v>77.37942911969246</v>
+      </c>
+      <c r="O60" s="21">
+        <v>79.899403773443638</v>
+      </c>
+      <c r="P60" s="21">
+        <v>72.339479812190092</v>
+      </c>
+      <c r="Q60" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34036,7 +34456,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34071,22 +34491,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -34182,28 +34602,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36914,6 +37334,50 @@
       </c>
       <c r="N59" s="17">
         <v>539172.84006657847</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-37743.814809844756</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-36015.091221200484</v>
+      </c>
+      <c r="I60" s="18">
+        <v>12234796.593900383</v>
+      </c>
+      <c r="J60" s="18">
+        <v>12822066.562043341</v>
+      </c>
+      <c r="K60" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L60" s="18">
+        <v>13398983.216919765</v>
+      </c>
+      <c r="M60" s="18">
+        <v>5123343.22362349</v>
+      </c>
+      <c r="N60" s="17">
+        <v>576916.65487642318</v>
       </c>
     </row>
   </sheetData>
@@ -36932,7 +37396,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36973,10 +37437,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -37063,28 +37527,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -39459,6 +39923,44 @@
       </c>
       <c r="L59" s="17">
         <v>878180.59993604012</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="18">
+        <v>12474978.130078416</v>
+      </c>
+      <c r="H60" s="18">
+        <v>13073776.806689657</v>
+      </c>
+      <c r="I60" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J60" s="18">
+        <v>14028882.557513656</v>
+      </c>
+      <c r="K60" s="18">
+        <v>4667547.7397862319</v>
+      </c>
+      <c r="L60" s="17">
+        <v>955105.75082399882</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -142,6 +146,18 @@
   </si>
   <si>
     <t>年化收益率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -647,7 +663,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -821,6 +837,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -830,7 +849,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1003,6 +1022,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1046,7 +1068,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1220,6 +1242,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1229,7 +1254,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1403,6 +1428,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1694672.7323658499</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1881997.8085183678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1445,7 +1473,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1619,6 +1647,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1628,7 +1659,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1802,6 +1833,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>536179.7028836261</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>723504.77903614403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,11 +1857,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528543104"/>
-        <c:axId val="529729792"/>
+        <c:axId val="561098752"/>
+        <c:axId val="561100288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528543104"/>
+        <c:axId val="561098752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1870,14 +1904,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529729792"/>
+        <c:crossAx val="561100288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529729792"/>
+        <c:axId val="561100288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1928,7 +1962,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528543104"/>
+        <c:crossAx val="561098752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2119,7 +2153,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2293,6 +2327,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2312,8 +2349,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="526537856"/>
-        <c:axId val="526531968"/>
+        <c:axId val="529930112"/>
+        <c:axId val="529928576"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2338,7 +2375,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2512,6 +2549,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2521,7 +2561,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2695,6 +2735,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2716,11 +2759,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526528896"/>
-        <c:axId val="526530432"/>
+        <c:axId val="528729216"/>
+        <c:axId val="528730752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526528896"/>
+        <c:axId val="528729216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2763,14 +2806,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526530432"/>
+        <c:crossAx val="528730752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526530432"/>
+        <c:axId val="528730752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,12 +2864,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526528896"/>
+        <c:crossAx val="528729216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526531968"/>
+        <c:axId val="529928576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2863,12 +2906,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526537856"/>
+        <c:crossAx val="529930112"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="526537856"/>
+        <c:axId val="529930112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2877,7 +2920,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526531968"/>
+        <c:crossAx val="529928576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3056,7 +3099,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3230,6 +3273,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3239,7 +3285,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3412,6 +3458,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3455,7 +3504,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3629,6 +3678,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3638,7 +3690,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3812,6 +3864,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>13398983.216919765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14977272.805961713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3854,7 +3909,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4028,6 +4083,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4037,7 +4095,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4211,6 +4269,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5123343.22362349</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6701632.8126654383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4232,11 +4293,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526561664"/>
-        <c:axId val="526563200"/>
+        <c:axId val="529958016"/>
+        <c:axId val="529959552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526561664"/>
+        <c:axId val="529958016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4279,14 +4340,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526563200"/>
+        <c:crossAx val="529959552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526563200"/>
+        <c:axId val="529959552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4337,7 +4398,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526561664"/>
+        <c:crossAx val="529958016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4528,7 +4589,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4702,6 +4763,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-37743.814809844756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-102248.30313182416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4721,8 +4785,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="527062528"/>
-        <c:axId val="527060992"/>
+        <c:axId val="530123008"/>
+        <c:axId val="530121472"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4747,7 +4811,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4921,6 +4985,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4930,7 +4997,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5104,6 +5171,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5125,11 +5195,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527053568"/>
-        <c:axId val="527055104"/>
+        <c:axId val="530093568"/>
+        <c:axId val="530095104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527053568"/>
+        <c:axId val="530093568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5172,14 +5242,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527055104"/>
+        <c:crossAx val="530095104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527055104"/>
+        <c:axId val="530095104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5230,12 +5300,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527053568"/>
+        <c:crossAx val="530093568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="527060992"/>
+        <c:axId val="530121472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5272,12 +5342,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527062528"/>
+        <c:crossAx val="530123008"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="527062528"/>
+        <c:axId val="530123008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5286,7 +5356,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="527060992"/>
+        <c:crossAx val="530121472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5465,7 +5535,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5639,6 +5709,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5648,7 +5721,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5821,6 +5894,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5864,7 +5940,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6038,6 +6114,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6047,7 +6126,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6221,6 +6300,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14028882.557513656</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15638155.580985475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6263,7 +6345,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6437,6 +6519,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6446,7 +6531,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6620,6 +6705,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4667547.7397862319</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6276820.7632580511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6641,11 +6729,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528098048"/>
-        <c:axId val="528099584"/>
+        <c:axId val="530253696"/>
+        <c:axId val="530255232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528098048"/>
+        <c:axId val="530253696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6688,14 +6776,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528099584"/>
+        <c:crossAx val="530255232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528099584"/>
+        <c:axId val="530255232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6746,7 +6834,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528098048"/>
+        <c:crossAx val="530253696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6937,7 +7025,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7111,6 +7199,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7130,8 +7221,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528484224"/>
-        <c:axId val="528482688"/>
+        <c:axId val="530791424"/>
+        <c:axId val="530789888"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7156,7 +7247,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7330,6 +7421,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7339,7 +7433,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7513,6 +7607,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7534,11 +7631,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528151680"/>
-        <c:axId val="528153216"/>
+        <c:axId val="530782464"/>
+        <c:axId val="530788352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528151680"/>
+        <c:axId val="530782464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7581,14 +7678,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528153216"/>
+        <c:crossAx val="530788352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528153216"/>
+        <c:axId val="530788352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7639,12 +7736,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528151680"/>
+        <c:crossAx val="530782464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="528482688"/>
+        <c:axId val="530789888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7681,12 +7778,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528484224"/>
+        <c:crossAx val="530791424"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528484224"/>
+        <c:axId val="530791424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7695,7 +7792,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528482688"/>
+        <c:crossAx val="530789888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7857,7 +7954,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8031,6 +8128,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8050,8 +8150,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="534055552"/>
-        <c:axId val="534054016"/>
+        <c:axId val="565532160"/>
+        <c:axId val="565530624"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8076,7 +8176,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8250,6 +8350,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8259,7 +8362,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8433,6 +8536,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8454,11 +8560,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="534049152"/>
-        <c:axId val="534051840"/>
+        <c:axId val="565526912"/>
+        <c:axId val="565528448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="534049152"/>
+        <c:axId val="565526912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8501,14 +8607,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534051840"/>
+        <c:crossAx val="565528448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="534051840"/>
+        <c:axId val="565528448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8559,12 +8665,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534049152"/>
+        <c:crossAx val="565526912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="534054016"/>
+        <c:axId val="565530624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8601,12 +8707,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534055552"/>
+        <c:crossAx val="565532160"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="534055552"/>
+        <c:axId val="565532160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8615,7 +8721,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="534054016"/>
+        <c:crossAx val="565530624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8794,7 +8900,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8968,6 +9074,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8977,7 +9086,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9150,6 +9259,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9193,7 +9305,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9367,6 +9479,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9376,7 +9491,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9550,6 +9665,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1906592.0501737606</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2130123.8005371881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9592,7 +9710,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9766,6 +9884,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9775,7 +9896,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9949,6 +10070,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>586700.45807416737</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>810232.20843759482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9970,11 +10094,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="534128128"/>
-        <c:axId val="534138880"/>
+        <c:axId val="565585408"/>
+        <c:axId val="565586944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="534128128"/>
+        <c:axId val="565585408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10017,14 +10141,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534138880"/>
+        <c:crossAx val="565586944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="534138880"/>
+        <c:axId val="565586944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10075,7 +10199,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534128128"/>
+        <c:crossAx val="565585408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10287,7 +10411,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10461,6 +10585,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-3486.2836718054768</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-6554.9847565695836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10480,8 +10607,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="535066112"/>
-        <c:axId val="535055744"/>
+        <c:axId val="565930624"/>
+        <c:axId val="565929088"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10506,7 +10633,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10680,6 +10807,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10689,7 +10819,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10863,6 +10993,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10884,11 +11017,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="534854656"/>
-        <c:axId val="535053056"/>
+        <c:axId val="565843072"/>
+        <c:axId val="565844992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="534854656"/>
+        <c:axId val="565843072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10931,14 +11064,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535053056"/>
+        <c:crossAx val="565844992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535053056"/>
+        <c:axId val="565844992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10989,12 +11122,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534854656"/>
+        <c:crossAx val="565843072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="535055744"/>
+        <c:axId val="565929088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11031,12 +11164,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535066112"/>
+        <c:crossAx val="565930624"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="535066112"/>
+        <c:axId val="565930624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11045,7 +11178,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="535055744"/>
+        <c:crossAx val="565929088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11224,7 +11357,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11398,6 +11531,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11407,7 +11543,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11580,6 +11716,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11623,7 +11762,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11797,6 +11936,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11806,7 +11948,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11980,6 +12122,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>16125218.576873584</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18043573.156056687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12022,7 +12167,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12196,6 +12341,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12205,7 +12353,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12379,6 +12527,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5237382.8033926059</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7155737.3825757094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12400,11 +12551,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535366272"/>
-        <c:axId val="535404928"/>
+        <c:axId val="566189056"/>
+        <c:axId val="566211328"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535366272"/>
+        <c:axId val="566189056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12447,14 +12598,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535404928"/>
+        <c:crossAx val="566211328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535404928"/>
+        <c:axId val="566211328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12505,7 +12656,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535366272"/>
+        <c:crossAx val="566189056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12717,7 +12868,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12891,6 +13042,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-15385.030177591741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-54389.65209982227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12910,8 +13064,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="535681664"/>
-        <c:axId val="535680128"/>
+        <c:axId val="567055488"/>
+        <c:axId val="566962048"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12936,7 +13090,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13110,6 +13264,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13119,7 +13276,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13293,6 +13450,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13314,11 +13474,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535532672"/>
-        <c:axId val="535534976"/>
+        <c:axId val="566397184"/>
+        <c:axId val="566960512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535532672"/>
+        <c:axId val="566397184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13361,14 +13521,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535534976"/>
+        <c:crossAx val="566960512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535534976"/>
+        <c:axId val="566960512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13419,12 +13579,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535532672"/>
+        <c:crossAx val="566397184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="535680128"/>
+        <c:axId val="566962048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13461,12 +13621,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535681664"/>
+        <c:crossAx val="567055488"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="535681664"/>
+        <c:axId val="567055488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13475,7 +13635,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="535680128"/>
+        <c:crossAx val="566962048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13654,7 +13814,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13828,6 +13988,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13837,7 +14000,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14010,6 +14173,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -14053,7 +14219,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14227,6 +14393,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14236,7 +14405,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14410,6 +14579,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>2127323.2568106027</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2383797.0624165004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14452,7 +14624,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14626,6 +14798,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14635,7 +14810,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14809,6 +14984,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>808227.66514269751</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1064701.4707485952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14830,11 +15008,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="536128896"/>
-        <c:axId val="536196608"/>
+        <c:axId val="567322496"/>
+        <c:axId val="567423360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="536128896"/>
+        <c:axId val="567322496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14877,14 +15055,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536196608"/>
+        <c:crossAx val="567423360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="536196608"/>
+        <c:axId val="567423360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14935,7 +15113,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536128896"/>
+        <c:crossAx val="567322496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15126,7 +15304,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15300,6 +15478,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-1051.0935769830185</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-2847.4210998735844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15319,8 +15500,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="526226176"/>
-        <c:axId val="526220288"/>
+        <c:axId val="467539456"/>
+        <c:axId val="467537920"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15345,7 +15526,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15519,6 +15700,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15528,7 +15712,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15702,6 +15886,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15723,11 +15910,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526217216"/>
-        <c:axId val="526218752"/>
+        <c:axId val="467501824"/>
+        <c:axId val="467503360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526217216"/>
+        <c:axId val="467501824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15770,14 +15957,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526218752"/>
+        <c:crossAx val="467503360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526218752"/>
+        <c:axId val="467503360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15828,12 +16015,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526217216"/>
+        <c:crossAx val="467501824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526220288"/>
+        <c:axId val="467537920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15870,12 +16057,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526226176"/>
+        <c:crossAx val="467539456"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="526226176"/>
+        <c:axId val="467539456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15884,7 +16071,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526220288"/>
+        <c:crossAx val="467537920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16063,7 +16250,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16237,6 +16424,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16246,7 +16436,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16419,6 +16609,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16462,7 +16655,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16636,6 +16829,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16645,7 +16841,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16819,6 +17015,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1721412.8570318066</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1912029.4197918652</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16861,7 +17060,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17035,6 +17234,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17044,7 +17246,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17218,6 +17420,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>546601.06113625411</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>737217.62389631267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17239,11 +17444,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526495744"/>
-        <c:axId val="526497280"/>
+        <c:axId val="528691968"/>
+        <c:axId val="528693504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526495744"/>
+        <c:axId val="528691968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17286,14 +17491,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526497280"/>
+        <c:crossAx val="528693504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526497280"/>
+        <c:axId val="528693504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17344,7 +17549,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526495744"/>
+        <c:crossAx val="528691968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18280,7 +18485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18411,28 +18616,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20845,6 +21050,44 @@
       </c>
       <c r="L60" s="29">
         <v>172838.83582129193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="32">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="31">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="29">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="29">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="30">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="30">
+        <v>1424285.4577023056</v>
+      </c>
+      <c r="H61" s="30">
+        <v>1676384.0489142279</v>
+      </c>
+      <c r="I61" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J61" s="30">
+        <v>1881997.8085183678</v>
+      </c>
+      <c r="K61" s="30">
+        <v>723504.77903614403</v>
+      </c>
+      <c r="L61" s="29">
+        <v>205613.75960413984</v>
       </c>
     </row>
   </sheetData>
@@ -20863,7 +21106,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20898,16 +21141,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20934,16 +21177,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -21005,28 +21248,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -24104,6 +24347,56 @@
         <v>67.160806984825626</v>
       </c>
       <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-6554.9847565695836</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-5569.2306725832077</v>
+      </c>
+      <c r="G61" s="18">
+        <v>1727234.1261785296</v>
+      </c>
+      <c r="H61" s="18">
+        <v>2032954.6455786328</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J61" s="18">
+        <v>2130123.8005371881</v>
+      </c>
+      <c r="K61" s="18">
+        <v>810232.20843759482</v>
+      </c>
+      <c r="L61" s="17">
+        <v>97169.154958555227</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -24123,7 +24416,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24158,16 +24451,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -24194,16 +24487,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24265,28 +24558,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27364,6 +27657,56 @@
         <v>67.160806984825626</v>
       </c>
       <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-54389.65209982227</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-46210.40780329454</v>
+      </c>
+      <c r="G61" s="18">
+        <v>14824747.516673513</v>
+      </c>
+      <c r="H61" s="18">
+        <v>17448728.50574781</v>
+      </c>
+      <c r="I61" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J61" s="18">
+        <v>18043573.156056687</v>
+      </c>
+      <c r="K61" s="18">
+        <v>7155737.3825757094</v>
+      </c>
+      <c r="L61" s="17">
+        <v>594844.65030887653</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -27383,7 +27726,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27418,22 +27761,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27460,16 +27803,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -27543,28 +27886,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30984,6 +31327,62 @@
         <v>67.160806984825626</v>
       </c>
       <c r="R60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-2847.4210998735844</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-2419.2191921244844</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1985748.7729419891</v>
+      </c>
+      <c r="J61" s="18">
+        <v>2337226.3966530859</v>
+      </c>
+      <c r="K61" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L61" s="18">
+        <v>2383797.0624165004</v>
+      </c>
+      <c r="M61" s="18">
+        <v>1064701.4707485952</v>
+      </c>
+      <c r="N61" s="17">
+        <v>46570.665763414443</v>
+      </c>
+      <c r="O61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="P61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="Q61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="R61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -31003,7 +31402,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31038,16 +31437,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -31074,19 +31473,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31164,28 +31563,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34437,6 +34836,59 @@
         <v>72.339479812190092</v>
       </c>
       <c r="Q60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="18">
+        <v>1449800.8443679775</v>
+      </c>
+      <c r="H61" s="18">
+        <v>1706415.6601877252</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J61" s="18">
+        <v>1912029.4197918652</v>
+      </c>
+      <c r="K61" s="18">
+        <v>737217.62389631267</v>
+      </c>
+      <c r="L61" s="17">
+        <v>205613.75960413984</v>
+      </c>
+      <c r="M61" s="21">
+        <v>96.011413524955756</v>
+      </c>
+      <c r="N61" s="21">
+        <v>83.590090588113569</v>
+      </c>
+      <c r="O61" s="21">
+        <v>81.129632711666943</v>
+      </c>
+      <c r="P61" s="21">
+        <v>88.511006341006805</v>
+      </c>
+      <c r="Q61" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34456,7 +34908,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34491,22 +34943,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -34602,28 +35054,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -37378,6 +37830,50 @@
       </c>
       <c r="N60" s="17">
         <v>576916.65487642318</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-102248.30313182416</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-86871.961899015572</v>
+      </c>
+      <c r="I61" s="18">
+        <v>12147924.632001366</v>
+      </c>
+      <c r="J61" s="18">
+        <v>14298107.847953467</v>
+      </c>
+      <c r="K61" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L61" s="18">
+        <v>14977272.805961713</v>
+      </c>
+      <c r="M61" s="18">
+        <v>6701632.8126654383</v>
+      </c>
+      <c r="N61" s="17">
+        <v>679164.95800824731</v>
       </c>
     </row>
   </sheetData>
@@ -37396,7 +37892,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37431,16 +37927,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -37527,28 +38023,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -39961,6 +40457,44 @@
       </c>
       <c r="L60" s="17">
         <v>955105.75082399882</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="18">
+        <v>12243926.091061944</v>
+      </c>
+      <c r="H61" s="18">
+        <v>14411101.569662364</v>
+      </c>
+      <c r="I61" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J61" s="18">
+        <v>15638155.580985475</v>
+      </c>
+      <c r="K61" s="18">
+        <v>6276820.7632580511</v>
+      </c>
+      <c r="L61" s="17">
+        <v>1227054.0113231102</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="31">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,15 +145,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
+    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -663,7 +655,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -840,6 +832,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -849,7 +844,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1025,6 +1020,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1068,7 +1066,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1245,6 +1243,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1254,7 +1255,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1431,6 +1432,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1881997.8085183678</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1978849.1612350328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1473,7 +1477,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1650,6 +1654,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1659,7 +1666,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1836,6 +1843,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>723504.77903614403</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>820356.13175280904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1857,11 +1867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561098752"/>
-        <c:axId val="561100288"/>
+        <c:axId val="401928960"/>
+        <c:axId val="401930496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561098752"/>
+        <c:axId val="401928960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1904,14 +1914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561100288"/>
+        <c:crossAx val="401930496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561100288"/>
+        <c:axId val="401930496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1962,7 +1972,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561098752"/>
+        <c:crossAx val="401928960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2153,7 +2163,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2330,6 +2340,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2349,8 +2362,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529930112"/>
-        <c:axId val="529928576"/>
+        <c:axId val="473132416"/>
+        <c:axId val="473130880"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2375,7 +2388,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2552,6 +2565,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2561,7 +2577,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2738,6 +2754,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2759,11 +2778,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528729216"/>
-        <c:axId val="528730752"/>
+        <c:axId val="473127552"/>
+        <c:axId val="473129344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528729216"/>
+        <c:axId val="473127552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,14 +2825,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528730752"/>
+        <c:crossAx val="473129344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528730752"/>
+        <c:axId val="473129344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,12 +2883,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528729216"/>
+        <c:crossAx val="473127552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529928576"/>
+        <c:axId val="473130880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2906,12 +2925,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529930112"/>
+        <c:crossAx val="473132416"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529930112"/>
+        <c:axId val="473132416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2920,7 +2939,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529928576"/>
+        <c:crossAx val="473130880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3099,7 +3118,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3276,6 +3295,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3285,7 +3307,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3461,6 +3483,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3504,7 +3529,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3681,6 +3706,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3690,7 +3718,7 @@
               <c:f>'模型二 (2)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3867,6 +3895,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14977272.805961713</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>15803331.182775768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3909,7 +3940,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4086,6 +4117,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4095,7 +4129,7 @@
               <c:f>'模型二 (2)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4272,6 +4306,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6701632.8126654383</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7527691.1894794926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4293,11 +4330,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529958016"/>
-        <c:axId val="529959552"/>
+        <c:axId val="479472256"/>
+        <c:axId val="479474048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529958016"/>
+        <c:axId val="479472256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4340,14 +4377,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529959552"/>
+        <c:crossAx val="479474048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529959552"/>
+        <c:axId val="479474048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4398,7 +4435,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529958016"/>
+        <c:crossAx val="479472256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4589,7 +4626,7 @@
               <c:f>'模型二 (2)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4766,6 +4803,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-102248.30313182416</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-228232.84251096987</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4785,8 +4825,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="530123008"/>
-        <c:axId val="530121472"/>
+        <c:axId val="479522816"/>
+        <c:axId val="479496448"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4811,7 +4851,7 @@
               <c:f>'模型二 (2)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4988,6 +5028,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4997,7 +5040,7 @@
               <c:f>'模型二 (2)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5174,6 +5217,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5195,11 +5241,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530093568"/>
-        <c:axId val="530095104"/>
+        <c:axId val="479489024"/>
+        <c:axId val="479494912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530093568"/>
+        <c:axId val="479489024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5242,14 +5288,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530095104"/>
+        <c:crossAx val="479494912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530095104"/>
+        <c:axId val="479494912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5300,12 +5346,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530093568"/>
+        <c:crossAx val="479489024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="530121472"/>
+        <c:axId val="479496448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5342,12 +5388,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530123008"/>
+        <c:crossAx val="479522816"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="530123008"/>
+        <c:axId val="479522816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5356,7 +5402,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="530121472"/>
+        <c:crossAx val="479496448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5535,7 +5581,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5712,6 +5758,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5721,7 +5770,7 @@
               <c:f>'模型二 (2)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5897,6 +5946,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5940,7 +5992,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6117,6 +6169,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6126,7 +6181,7 @@
               <c:f>'模型二 (2)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6303,6 +6358,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15638155.580985475</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16470742.053078819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6345,7 +6403,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6522,6 +6580,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6531,7 +6592,7 @@
               <c:f>'模型二 (2)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6708,6 +6769,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6276820.7632580511</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7109407.2353513949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6729,11 +6793,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530253696"/>
-        <c:axId val="530255232"/>
+        <c:axId val="480177152"/>
+        <c:axId val="494867200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530253696"/>
+        <c:axId val="480177152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6776,14 +6840,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530255232"/>
+        <c:crossAx val="494867200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530255232"/>
+        <c:axId val="494867200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6834,7 +6898,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530253696"/>
+        <c:crossAx val="480177152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7025,7 +7089,7 @@
               <c:f>'模型二 (2)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7202,6 +7266,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7221,8 +7288,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="530791424"/>
-        <c:axId val="530789888"/>
+        <c:axId val="494907776"/>
+        <c:axId val="494893696"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7247,7 +7314,7 @@
               <c:f>'模型二 (2)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7424,6 +7491,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7433,7 +7503,7 @@
               <c:f>'模型二 (2)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7610,6 +7680,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7631,11 +7704,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530782464"/>
-        <c:axId val="530788352"/>
+        <c:axId val="494886272"/>
+        <c:axId val="494892160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530782464"/>
+        <c:axId val="494886272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7678,14 +7751,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530788352"/>
+        <c:crossAx val="494892160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530788352"/>
+        <c:axId val="494892160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7736,12 +7809,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530782464"/>
+        <c:crossAx val="494886272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="530789888"/>
+        <c:axId val="494893696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7778,12 +7851,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530791424"/>
+        <c:crossAx val="494907776"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="530791424"/>
+        <c:axId val="494907776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7792,7 +7865,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="530789888"/>
+        <c:crossAx val="494893696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7954,7 +8027,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8131,6 +8204,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8150,8 +8226,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="565532160"/>
-        <c:axId val="565530624"/>
+        <c:axId val="546469760"/>
+        <c:axId val="546467840"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8176,7 +8252,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8353,6 +8429,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8362,7 +8441,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8539,6 +8618,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8560,11 +8642,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565526912"/>
-        <c:axId val="565528448"/>
+        <c:axId val="546463744"/>
+        <c:axId val="546466048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565526912"/>
+        <c:axId val="546463744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8607,14 +8689,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565528448"/>
+        <c:crossAx val="546466048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565528448"/>
+        <c:axId val="546466048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8665,12 +8747,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565526912"/>
+        <c:crossAx val="546463744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="565530624"/>
+        <c:axId val="546467840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8707,12 +8789,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565532160"/>
+        <c:crossAx val="546469760"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="565532160"/>
+        <c:axId val="546469760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8721,7 +8803,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="565530624"/>
+        <c:crossAx val="546467840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8900,7 +8982,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9077,6 +9159,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9086,7 +9171,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9262,6 +9347,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9305,7 +9393,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9482,6 +9570,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9491,7 +9582,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9668,6 +9759,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2130123.8005371881</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2247575.650286919</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9710,7 +9804,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9887,6 +9981,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9896,7 +9993,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10073,6 +10170,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>810232.20843759482</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>927684.05818732572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10094,11 +10194,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565585408"/>
-        <c:axId val="565586944"/>
+        <c:axId val="556770432"/>
+        <c:axId val="556771968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565585408"/>
+        <c:axId val="556770432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10141,14 +10241,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565586944"/>
+        <c:crossAx val="556771968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565586944"/>
+        <c:axId val="556771968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10199,7 +10299,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565585408"/>
+        <c:crossAx val="556770432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10411,7 +10511,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10588,6 +10688,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-6554.9847565695836</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10607,8 +10710,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="565930624"/>
-        <c:axId val="565929088"/>
+        <c:axId val="571171968"/>
+        <c:axId val="571059584"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10633,7 +10736,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10810,6 +10913,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10819,7 +10925,7 @@
               <c:f>'模型二 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10996,6 +11102,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11017,11 +11126,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565843072"/>
-        <c:axId val="565844992"/>
+        <c:axId val="571056128"/>
+        <c:axId val="571057664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565843072"/>
+        <c:axId val="571056128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11064,14 +11173,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565844992"/>
+        <c:crossAx val="571057664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565844992"/>
+        <c:axId val="571057664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11122,12 +11231,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565843072"/>
+        <c:crossAx val="571056128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="565929088"/>
+        <c:axId val="571059584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11164,12 +11273,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565930624"/>
+        <c:crossAx val="571171968"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="565930624"/>
+        <c:axId val="571171968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11178,7 +11287,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="565929088"/>
+        <c:crossAx val="571059584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11357,7 +11466,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11534,6 +11643,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11543,7 +11655,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11719,6 +11831,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11762,7 +11877,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11939,6 +12054,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11948,7 +12066,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12125,6 +12243,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>18043573.156056687</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19051655.379257303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12167,7 +12288,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12344,6 +12465,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12353,7 +12477,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12530,6 +12654,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>7155737.3825757094</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8163819.6057763249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12551,11 +12678,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566189056"/>
-        <c:axId val="566211328"/>
+        <c:axId val="571383168"/>
+        <c:axId val="571475456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566189056"/>
+        <c:axId val="571383168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12598,14 +12725,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566211328"/>
+        <c:crossAx val="571475456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566211328"/>
+        <c:axId val="571475456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12656,7 +12783,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566189056"/>
+        <c:crossAx val="571383168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12868,7 +12995,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13045,6 +13172,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-54389.65209982227</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13064,8 +13194,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="567055488"/>
-        <c:axId val="566962048"/>
+        <c:axId val="573039360"/>
+        <c:axId val="572984320"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13090,7 +13220,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13267,6 +13397,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13276,7 +13409,7 @@
               <c:f>'模型二 (2)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13453,6 +13586,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13474,11 +13610,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566397184"/>
-        <c:axId val="566960512"/>
+        <c:axId val="572972032"/>
+        <c:axId val="572982784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566397184"/>
+        <c:axId val="572972032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13521,14 +13657,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566960512"/>
+        <c:crossAx val="572982784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566960512"/>
+        <c:axId val="572982784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13579,12 +13715,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566397184"/>
+        <c:crossAx val="572972032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566962048"/>
+        <c:axId val="572984320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13621,12 +13757,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567055488"/>
+        <c:crossAx val="573039360"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="567055488"/>
+        <c:axId val="573039360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13635,7 +13771,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566962048"/>
+        <c:crossAx val="572984320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13814,7 +13950,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13991,6 +14127,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14000,7 +14139,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14176,6 +14315,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -14219,7 +14361,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14396,6 +14538,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14405,7 +14550,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14582,6 +14727,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2383797.0624165004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2518827.8975449791</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14624,7 +14772,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14801,6 +14949,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14810,7 +14961,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14987,6 +15138,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1064701.4707485952</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1199732.3058770739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15008,11 +15162,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567322496"/>
-        <c:axId val="567423360"/>
+        <c:axId val="573676928"/>
+        <c:axId val="573854848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567322496"/>
+        <c:axId val="573676928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15055,14 +15209,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567423360"/>
+        <c:crossAx val="573854848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="567423360"/>
+        <c:axId val="573854848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15113,7 +15267,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567322496"/>
+        <c:crossAx val="573676928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15304,7 +15458,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15481,6 +15635,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-2847.4210998735844</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-31779.256552160365</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15500,8 +15657,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="467539456"/>
-        <c:axId val="467537920"/>
+        <c:axId val="470891520"/>
+        <c:axId val="470889984"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15526,7 +15683,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15703,6 +15860,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15712,7 +15872,7 @@
               <c:f>'模型二 (2)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15889,6 +16049,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15910,11 +16073,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467501824"/>
-        <c:axId val="467503360"/>
+        <c:axId val="470825216"/>
+        <c:axId val="470888448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467501824"/>
+        <c:axId val="470825216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15957,14 +16120,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467503360"/>
+        <c:crossAx val="470888448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467503360"/>
+        <c:axId val="470888448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16015,12 +16178,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467501824"/>
+        <c:crossAx val="470825216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="467537920"/>
+        <c:axId val="470889984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16057,12 +16220,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467539456"/>
+        <c:crossAx val="470891520"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="467539456"/>
+        <c:axId val="470891520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16071,7 +16234,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="467537920"/>
+        <c:crossAx val="470889984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16250,7 +16413,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16427,6 +16590,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16436,7 +16602,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16612,6 +16778,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16655,7 +16824,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16832,6 +17001,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16841,7 +17013,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17018,6 +17190,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1912029.4197918652</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2010615.8177554612</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17060,7 +17235,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17237,6 +17412,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17246,7 +17424,7 @@
               <c:f>'模型二 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17423,6 +17601,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>737217.62389631267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>835804.02185990871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17444,11 +17625,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528691968"/>
-        <c:axId val="528693504"/>
+        <c:axId val="472271104"/>
+        <c:axId val="473112576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528691968"/>
+        <c:axId val="472271104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17491,14 +17672,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528693504"/>
+        <c:crossAx val="473112576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528693504"/>
+        <c:axId val="473112576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17549,7 +17730,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528691968"/>
+        <c:crossAx val="472271104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18485,7 +18666,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18616,28 +18797,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -21088,6 +21269,44 @@
       </c>
       <c r="L61" s="29">
         <v>205613.75960413984</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="32">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="31">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="29">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="29">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="30">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="30">
+        <v>1395323.7175117971</v>
+      </c>
+      <c r="H62" s="30">
+        <v>1737178.0349556094</v>
+      </c>
+      <c r="I62" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J62" s="30">
+        <v>1978849.1612350328</v>
+      </c>
+      <c r="K62" s="30">
+        <v>820356.13175280904</v>
+      </c>
+      <c r="L62" s="29">
+        <v>241671.12627942342</v>
       </c>
     </row>
   </sheetData>
@@ -21106,7 +21325,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21141,16 +21360,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -21177,16 +21396,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="P1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -21248,28 +21467,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -24398,6 +24617,56 @@
       </c>
       <c r="P61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="18">
+        <v>1698272.385988021</v>
+      </c>
+      <c r="H62" s="18">
+        <v>2114349.1286530802</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2247575.650286919</v>
+      </c>
+      <c r="K62" s="18">
+        <v>927684.05818732572</v>
+      </c>
+      <c r="L62" s="17">
+        <v>133226.5216338388</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24416,7 +24685,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24451,16 +24720,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -24487,16 +24756,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="P1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24558,28 +24827,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27708,6 +27977,56 @@
       </c>
       <c r="P61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>14560371.798799217</v>
+      </c>
+      <c r="H62" s="18">
+        <v>18127662.958934288</v>
+      </c>
+      <c r="I62" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J62" s="18">
+        <v>19051655.379257303</v>
+      </c>
+      <c r="K62" s="18">
+        <v>8163819.6057763249</v>
+      </c>
+      <c r="L62" s="17">
+        <v>923992.42032301589</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27726,7 +28045,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27761,22 +28080,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27803,16 +28122,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="R1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="Q1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -27886,28 +28205,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -31384,6 +31703,62 @@
       </c>
       <c r="R61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-31779.256552160365</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-25525.507173048401</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1960223.2657689408</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2440477.9752294044</v>
+      </c>
+      <c r="K62" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L62" s="18">
+        <v>2518827.8975449791</v>
+      </c>
+      <c r="M62" s="18">
+        <v>1199732.3058770739</v>
+      </c>
+      <c r="N62" s="17">
+        <v>78349.922315574804</v>
+      </c>
+      <c r="O62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -31402,7 +31777,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31437,16 +31812,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -31473,19 +31848,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="P1" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="Q1" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="P1" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31563,28 +31938,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34889,6 +35264,59 @@
         <v>88.511006341006805</v>
       </c>
       <c r="Q61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="18">
+        <v>1420839.1041774689</v>
+      </c>
+      <c r="H62" s="18">
+        <v>1768944.6914760377</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2010615.8177554612</v>
+      </c>
+      <c r="K62" s="18">
+        <v>835804.02185990871</v>
+      </c>
+      <c r="L62" s="17">
+        <v>241671.12627942342</v>
+      </c>
+      <c r="M62" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N62" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O62" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P62" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q62" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34908,7 +35336,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34943,22 +35371,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -35054,28 +35482,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -37874,6 +38302,50 @@
       </c>
       <c r="N61" s="17">
         <v>679164.95800824731</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-228232.84251096987</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-183319.55151552943</v>
+      </c>
+      <c r="I62" s="18">
+        <v>11964605.080485838</v>
+      </c>
+      <c r="J62" s="18">
+        <v>14895933.382256551</v>
+      </c>
+      <c r="K62" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L62" s="18">
+        <v>15803331.182775768</v>
+      </c>
+      <c r="M62" s="18">
+        <v>7527691.1894794926</v>
+      </c>
+      <c r="N62" s="17">
+        <v>907397.80051921715</v>
       </c>
     </row>
   </sheetData>
@@ -37892,7 +38364,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37927,16 +38399,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -38023,28 +38495,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -40495,6 +40967,44 @@
       </c>
       <c r="L61" s="17">
         <v>1227054.0113231102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>11979550.373187648</v>
+      </c>
+      <c r="H62" s="18">
+        <v>14914540.271741569</v>
+      </c>
+      <c r="I62" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J62" s="18">
+        <v>16470742.053078819</v>
+      </c>
+      <c r="K62" s="18">
+        <v>7109407.2353513949</v>
+      </c>
+      <c r="L62" s="17">
+        <v>1556201.7813372496</v>
       </c>
     </row>
   </sheetData>
